--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -701,31 +701,31 @@
       <c r="E1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F1" t="n">
+      <c r="F1" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N1" t="n">
+      <c r="H1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -755,7 +755,7 @@
           <t>StaminaCost</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>StaminaCostType</t>
         </is>
@@ -765,37 +765,37 @@
           <t>MinRequiredStamina</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>SprintRestartStaminaPercent</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>ActionType</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>Cooldown</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>InputBufferTime</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>bLocksMovement</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>bUsesRootMotion</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>bCanBeInterrupted</t>
         </is>
@@ -819,7 +819,7 @@
       <c r="E3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Instant</t>
         </is>
@@ -827,10 +827,10 @@
       <c r="G3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>LightAttack</t>
         </is>
@@ -854,7 +854,7 @@
       <c r="E4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Instant</t>
         </is>
@@ -862,10 +862,10 @@
       <c r="G4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>HeavyAttack</t>
         </is>
@@ -889,7 +889,7 @@
       <c r="E5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>Instant</t>
         </is>
@@ -897,10 +897,10 @@
       <c r="G5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>Guard</t>
         </is>
@@ -924,7 +924,7 @@
       <c r="E6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>PerSecond</t>
         </is>
@@ -932,10 +932,10 @@
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
@@ -959,7 +959,7 @@
       <c r="E7" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>Instant</t>
         </is>
@@ -967,10 +967,10 @@
       <c r="G7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>DodgeRoll</t>
         </is>
@@ -1023,25 +1023,25 @@
       <c r="E1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F1" t="n">
+      <c r="F1" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1" t="n">
+      <c r="H1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
           <t>CombatStance</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>WeaponType</t>
         </is>
@@ -1081,27 +1081,27 @@
           <t>Montage</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>StartSection</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>PlayRate</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>BlendIn</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>BlendOut</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>bUseRootMotion</t>
         </is>
@@ -1125,22 +1125,26 @@
           <t>Relaxed</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>/Game/Character/Player/Animation/Montages/AM_DodgeRoll_Relaxed_Any.AM_DodgeRoll_Relaxed_Any</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="L3" t="b">
+      <c r="L3" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1185,7 +1189,7 @@
       <c r="E1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F1" t="n">
+      <c r="F1" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="n">
@@ -1218,7 +1222,7 @@
           <t>StartTime</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>EndTime</t>
         </is>
@@ -1245,7 +1249,7 @@
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n"/>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -975,6 +975,18 @@
           <t>DodgeRoll</t>
         </is>
       </c>
+      <c r="J7" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1145,7 +1157,7 @@
         <v>0.1</v>
       </c>
       <c r="L3" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1159,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.6640625" customWidth="1" style="2" min="1" max="1"/>
@@ -1247,12 +1259,50 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="n">
+        <v>40022</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>30021</v>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>InterruptLock</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n"/>
+      <c r="F4" s="0" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>40023</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30021</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>InputBuffer</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -5,11 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Moveset" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="ActionData" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="ActionData" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Moveset" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="ActionAnimationData" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="ActionWindowData" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
@@ -34,6 +34,72 @@
     <t xml:space="preserve">Tid</t>
   </si>
   <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaCostType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinRequiredStamina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SprintRestartStaminaPercent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActionType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InputBufferTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bLocksMovement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bUsesRootMotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bCanBeInterrupted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LightAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeavyAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PerSecond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DodgeRoll</t>
+  </si>
+  <si>
     <t xml:space="preserve">설명</t>
   </si>
   <si>
@@ -64,9 +130,6 @@
     <t xml:space="preserve">Default</t>
   </si>
   <si>
-    <t xml:space="preserve">LightAttack</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relaxed</t>
   </si>
   <si>
@@ -76,70 +139,7 @@
     <t xml:space="preserve">Any</t>
   </si>
   <si>
-    <t xml:space="preserve">HeavyAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guard</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StaminaCost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StaminaCostType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MinRequiredStamina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SprintRestartStaminaPercent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActionType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooldown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InputBufferTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bLocksMovement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bUsesRootMotion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bCanBeInterrupted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PerSecond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DodgeRoll</t>
   </si>
   <si>
     <t xml:space="preserve">Montage</t>
@@ -227,20 +227,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="1"/>
@@ -249,6 +236,19 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -319,59 +319,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -379,11 +379,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -391,7 +391,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -399,15 +399,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -427,15 +427,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -688,216 +688,288 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="7.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="13.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.83"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="2" width="7.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="19.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="11.62"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="4" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="n">
+      <c r="B1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" s="7" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8" t="n">
+        <v>10001</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="n">
-        <v>20001</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="I3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8" t="n">
+        <v>10002</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="n">
+        <v>10011</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="8" t="n">
+        <v>10020</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="n">
+        <v>10021</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>10001</v>
-      </c>
-      <c r="K3" s="2" t="n">
+      <c r="F7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="n">
-        <v>20002</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>10002</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="n">
-        <v>20011</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>10011</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="n">
-        <v>20021</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>10021</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="M7" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="N7" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -911,46 +983,43 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="7.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="6.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="11.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="17.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="14.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="20.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="23.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="28.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="10.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="12.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="17.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="6" width="16.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="18.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="19.82"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="6" width="11.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="8.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="10" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="17.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="10" width="16.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="10" width="18.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="13.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="10" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="9" width="13.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="10" width="12.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="10" width="6.83"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="9" width="7.68"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="7" t="n">
+      <c r="B1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F1" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G1" s="7" t="n">
+      <c r="G1" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H1" s="3" t="n">
@@ -965,234 +1034,165 @@
       <c r="K1" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N1" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" s="10" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9" t="s">
+    </row>
+    <row r="2" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="D2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="E2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="F2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="G2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="H2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="I2" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11" t="n">
+      <c r="J2" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="n">
+        <v>20001</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="9" t="n">
         <v>10001</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="n">
+      <c r="K3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11" t="n">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="n">
+        <v>20002</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="9" t="n">
         <v>10002</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="n">
+      <c r="K4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11" t="n">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="n">
+        <v>20011</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="9" t="n">
         <v>10011</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="K5" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="9" t="n">
+        <v>20021</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="n">
+      <c r="E6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>10021</v>
+      </c>
+      <c r="K6" s="9" t="n">
         <v>0</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="11" t="n">
-        <v>10020</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11" t="n">
-        <v>10021</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="2" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="M7" s="2" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
@@ -1209,19 +1209,19 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="7.6953125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="14.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="6" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="18.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="16.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="25.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="6" width="12.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="6" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="6" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.87"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="12" width="7.69"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
@@ -1267,16 +1267,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G2" s="16" t="s">
         <v>39</v>
@@ -1306,13 +1306,13 @@
         <v>10021</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>45</v>
@@ -1320,49 +1320,49 @@
       <c r="H3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1" t="n">
+      <c r="I3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="L3" s="1" t="b">
+      <c r="L3" s="10" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="1" t="n">
         <v>30022</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="1" t="n">
         <v>10021</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>47</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="G4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="L4" s="1" t="b">
+      <c r="L4" s="10" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1386,35 +1386,35 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="7.6953125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="7.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="22.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="18.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="17.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.01"/>
   </cols>
   <sheetData>
     <row r="1" s="24" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="7" t="n">
+      <c r="B1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F1" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G1" s="7" t="n">
+      <c r="G1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1422,22 +1422,22 @@
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1499,10 +1499,10 @@
       <c r="G5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="1" t="n">
         <v>40024</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="1" t="n">
         <v>30022</v>
       </c>
       <c r="D6" s="28" t="s">
@@ -1516,10 +1516,10 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="1" t="n">
         <v>40025</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="1" t="n">
         <v>30022</v>
       </c>
       <c r="D7" s="29" t="s">
@@ -1533,10 +1533,10 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="1" t="n">
         <v>40026</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="1" t="n">
         <v>30022</v>
       </c>
       <c r="D8" s="30" t="s">

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="58">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -142,6 +142,9 @@
     <t xml:space="preserve">Dodge</t>
   </si>
   <si>
+    <t xml:space="preserve">Dash</t>
+  </si>
+  <si>
     <t xml:space="preserve">Montage</t>
   </si>
   <si>
@@ -160,16 +163,16 @@
     <t xml:space="preserve">bUseRootMotion</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/AM_Roll_Relaxed_Forward.AM_Roll_Relaxed_Forward</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Forward.AM_Roll_Relaxed_Forward</t>
   </si>
   <si>
     <t xml:space="preserve">Backward</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/AM_Roll_Relaxed_Backward.AM_Roll_Relaxed_Backward</t>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Backward.AM_Roll_Relaxed_Backward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_Forward.AM_Dodge_Relaxed_Forward</t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -395,44 +398,44 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -983,7 +986,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="7.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.6"/>
@@ -1190,6 +1193,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="10" t="n">
+        <v>20022</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>10021</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1206,7 +1238,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="7.6953125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.3"/>
@@ -1279,22 +1311,22 @@
         <v>30</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1315,11 +1347,9 @@
         <v>37</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="20" t="s">
         <v>46</v>
       </c>
+      <c r="H3" s="10"/>
       <c r="I3" s="10" t="n">
         <v>1</v>
       </c>
@@ -1341,7 +1371,7 @@
       <c r="C4" s="1" t="n">
         <v>10021</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>47</v>
       </c>
       <c r="E4" s="19" t="s">
@@ -1350,7 +1380,7 @@
       <c r="F4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>48</v>
       </c>
       <c r="I4" s="1" t="n">
@@ -1363,6 +1393,39 @@
         <v>0.1</v>
       </c>
       <c r="L4" s="10" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
+        <v>30023</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>10021</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" s="10" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1395,7 +1458,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.01"/>
   </cols>
   <sheetData>
-    <row r="1" s="24" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="23" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1411,76 +1474,76 @@
       <c r="E1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F1" s="23" t="n">
+      <c r="F1" s="22" t="n">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
+    <row r="2" s="25" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28" t="n">
+      <c r="A3" s="26"/>
+      <c r="B3" s="27" t="n">
         <v>40021</v>
       </c>
-      <c r="C3" s="28" t="n">
+      <c r="C3" s="27" t="n">
         <v>30021</v>
       </c>
-      <c r="D3" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="28" t="n">
+      <c r="D3" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="27" t="n">
         <v>0.1</v>
       </c>
-      <c r="F3" s="29" t="n">
+      <c r="F3" s="28" t="n">
         <v>0.55</v>
       </c>
-      <c r="G3" s="27"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20"/>
-      <c r="B4" s="29" t="n">
+      <c r="A4" s="29"/>
+      <c r="B4" s="28" t="n">
         <v>40022</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="28" t="n">
         <v>30021</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="29" t="n">
+      <c r="D4" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="28" t="n">
         <v>0.8</v>
       </c>
-      <c r="G4" s="20"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="30" t="n">
         <v>40023</v>
       </c>
@@ -1488,7 +1551,7 @@
         <v>30021</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="30" t="n">
         <v>0.55</v>
@@ -1496,7 +1559,7 @@
       <c r="F5" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="G5" s="20"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="n">
@@ -1505,13 +1568,13 @@
       <c r="C6" s="1" t="n">
         <v>30022</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="28" t="n">
+      <c r="D6" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="27" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="28" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -1522,13 +1585,13 @@
       <c r="C7" s="1" t="n">
         <v>30022</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="29" t="n">
+      <c r="D7" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="28" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1540,7 +1603,7 @@
         <v>30022</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>0.55</v>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="59">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -97,9 +97,15 @@
     <t xml:space="preserve">PerSecond</t>
   </si>
   <si>
+    <t xml:space="preserve">Roll</t>
+  </si>
+  <si>
     <t xml:space="preserve">DodgeRoll</t>
   </si>
   <si>
+    <t xml:space="preserve">Dodge</t>
+  </si>
+  <si>
     <t xml:space="preserve">설명</t>
   </si>
   <si>
@@ -137,9 +143,6 @@
   </si>
   <si>
     <t xml:space="preserve">Any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dodge</t>
   </si>
   <si>
     <t xml:space="preserve">Dash</t>
@@ -317,13 +320,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -331,53 +334,81 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -387,6 +418,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -691,7 +726,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.11"/>
@@ -701,8 +736,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.81"/>
@@ -951,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>0.8</v>
@@ -966,6 +1001,47 @@
         <v>1</v>
       </c>
       <c r="N7" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
+        <v>10022</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="9" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="9" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -989,236 +1065,236 @@
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="7.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="8.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="10" width="10.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="17.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="10" width="16.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="10" width="18.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="10" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="9" width="13.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="10" width="12.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="10" width="6.83"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="9" width="7.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="5.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="8.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="17.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="16.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="18.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="13.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="13.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="12.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="12" width="6.83"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="13" width="7.68"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="n">
+      <c r="B1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="D1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" s="16" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="11" t="s">
+      <c r="C2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="13" t="n">
+        <v>20001</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>10001</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="13" t="n">
+        <v>20002</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>10002</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13" t="n">
+        <v>20011</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>10011</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="13" t="n">
+        <v>20021</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="9" t="n">
-        <v>20001</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="F6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="G6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>10021</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="n">
+        <v>20022</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="9" t="n">
-        <v>10001</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="n">
-        <v>20002</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>10002</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="9" t="n">
-        <v>20011</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>10011</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="9" t="n">
-        <v>20021</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="G7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>10021</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="n">
-        <v>20022</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="H7" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>10021</v>
-      </c>
-      <c r="K7" s="10" t="n">
+      <c r="I7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>10022</v>
+      </c>
+      <c r="K7" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1241,191 +1317,191 @@
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="7.6953125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.87"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="12" width="7.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="17" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="18.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="16.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="25.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="17" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="17" width="10.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="18" width="7.69"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+    <row r="1" s="21" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L1" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="16" t="s">
+      <c r="B1" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" s="25" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="17" t="s">
+      <c r="G2" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="H2" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="I2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="J2" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="K2" s="24" t="s">
         <v>45</v>
       </c>
+      <c r="L2" s="24" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26" t="n">
         <v>30021</v>
       </c>
-      <c r="C3" s="18" t="n">
+      <c r="C3" s="26" t="n">
         <v>10021</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L3" s="12" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="17" t="n">
+        <v>30022</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>10021</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="10" t="n">
+      <c r="F4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="K3" s="10" t="n">
+      <c r="K4" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="L3" s="10" t="b">
+      <c r="L4" s="12" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="n">
-        <v>30022</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="10" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="17" t="n">
+        <v>30023</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>10022</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1" t="n">
+      <c r="F5" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K5" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="L4" s="10" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
-        <v>30023</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L5" s="10" t="b">
+      <c r="L5" s="12" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1446,19 +1522,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="7.6953125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="7.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="22.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="18.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="17.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="11.01"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="31" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1474,141 +1550,192 @@
       <c r="E1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F1" s="22" t="n">
+      <c r="F1" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="25" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
+    <row r="2" s="33" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="6" t="s">
         <v>53</v>
       </c>
+      <c r="F2" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="G2" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27" t="n">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35" t="n">
         <v>40021</v>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="C3" s="35" t="n">
         <v>30021</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="27" t="n">
+      <c r="D3" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="F3" s="28" t="n">
+      <c r="F3" s="36" t="n">
         <v>0.55</v>
       </c>
-      <c r="G3" s="26"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29"/>
-      <c r="B4" s="28" t="n">
+      <c r="A4" s="37"/>
+      <c r="B4" s="36" t="n">
         <v>40022</v>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="36" t="n">
         <v>30021</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="37"/>
+      <c r="B5" s="38" t="n">
+        <v>40023</v>
+      </c>
+      <c r="C5" s="38" t="n">
+        <v>30021</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="38" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F5" s="38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="17" t="n">
+        <v>40024</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>30022</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E6" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="17" t="n">
+        <v>40025</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>30022</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F7" s="36" t="n">
         <v>0.8</v>
       </c>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29"/>
-      <c r="B5" s="30" t="n">
-        <v>40023</v>
-      </c>
-      <c r="C5" s="30" t="n">
-        <v>30021</v>
-      </c>
-      <c r="D5" s="30" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="17" t="n">
+        <v>40026</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>30022</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="38" t="n">
+        <v>40027</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>30023</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="17" t="n">
+        <v>40028</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>30023</v>
+      </c>
+      <c r="D10" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E10" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="17" t="n">
+        <v>40029</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>30023</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="38" t="n">
         <v>0.55</v>
       </c>
-      <c r="F5" s="30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
-        <v>40024</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>30022</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
-        <v>40025</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>30022</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
-        <v>40026</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>30022</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F8" s="30" t="n">
+      <c r="F11" s="38" t="n">
         <v>0.8</v>
       </c>
     </row>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="57">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -169,70 +169,7 @@
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Forward.AM_Roll_Relaxed_Forward</t>
   </si>
   <si>
-    <t xml:space="preserve">Backward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Backward.AM_Roll_Relaxed_Backward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Left.AM_Roll_Relaxed_Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Right.AM_Roll_Relaxed_Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForwardLeft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_ForwardLeft.AM_Roll_Relaxed_ForwardLeft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForwardRight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_ForwardRight.AM_Roll_Relaxed_ForwardRight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackwardLeft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_BackwardLeft.AM_Roll_Relaxed_BackwardLeft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackwardRight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_BackwardRight.AM_Roll_Relaxed_BackwardRight</t>
-  </si>
-  <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_Forward.AM_Dodge_Relaxed_Forward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_Backward.AM_Dodge_Relaxed_Backward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_Left.AM_Dodge_Relaxed_Left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_Right.AM_Dodge_Relaxed_Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_FordwardLeft.AM_Dodge_Relaxed_FordwardLeft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_ForwardRight.AM_Dodge_Relaxed_ForwardRight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_BackwardLeft.AM_Dodge_Relaxed_BackwardLeft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_BackwardRight.AM_Dodge_Relaxed_BackwardRight</t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -377,7 +314,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -490,15 +427,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1502,237 +1435,60 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="17" t="n">
-        <v>30022</v>
-      </c>
-      <c r="C4" s="17" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K4" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L4" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="D4" s="28"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0"/>
-      <c r="B5" s="27" t="n">
-        <v>30023</v>
-      </c>
-      <c r="C5" s="27" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>51</v>
-      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="0"/>
       <c r="H5" s="0"/>
-      <c r="I5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L5" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17" t="n">
-        <v>30024</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K6" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L6" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="E6" s="27"/>
+      <c r="F6" s="12"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="n">
-        <v>30025</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L7" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17" t="n">
-        <v>30026</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L8" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="12"/>
+      <c r="L8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="n">
-        <v>30027</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L9" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="n">
-        <v>30028</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>10021</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="B10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="12"/>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="n">
@@ -1751,7 +1507,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="I11" s="17" t="n">
         <v>1</v>
@@ -18140,105 +17896,32 @@
       <c r="XFD11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="n">
-        <v>30030</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>10022</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L12" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="B12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17" t="n">
-        <v>30031</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>10022</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L13" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="D13" s="0"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="12"/>
+      <c r="L13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0"/>
-      <c r="B14" s="27" t="n">
-        <v>30032</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>10022</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>65</v>
-      </c>
+      <c r="B14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="0"/>
       <c r="H14" s="0"/>
-      <c r="I14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L14" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
@@ -34613,136 +34296,32 @@
       <c r="XFD14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="17" t="n">
-        <v>30033</v>
-      </c>
-      <c r="C15" s="17" t="n">
-        <v>10022</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L15" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="12"/>
+      <c r="L15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="n">
-        <v>30034</v>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>10022</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L16" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="B16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="17" t="n">
-        <v>30035</v>
-      </c>
-      <c r="C17" s="17" t="n">
-        <v>10022</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="12"/>
+      <c r="L17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="27" t="n">
-        <v>30036</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>10022</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L18" s="12" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
+      <c r="B18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="27"/>
@@ -34777,7 +34356,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="11.01"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="31" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -34793,92 +34372,92 @@
       <c r="E1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F1" s="31" t="n">
+      <c r="F1" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="34" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="33" t="s">
+    <row r="2" s="33" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="35"/>
-      <c r="B3" s="36" t="n">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35" t="n">
         <v>40021</v>
       </c>
-      <c r="C3" s="36" t="n">
+      <c r="C3" s="35" t="n">
         <v>30021</v>
       </c>
-      <c r="D3" s="36" t="s">
-        <v>75</v>
+      <c r="D3" s="35" t="s">
+        <v>54</v>
       </c>
-      <c r="E3" s="36" t="n">
+      <c r="E3" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="F3" s="37" t="n">
+      <c r="F3" s="36" t="n">
         <v>0.55</v>
       </c>
-      <c r="G3" s="35"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38"/>
-      <c r="B4" s="37" t="n">
+      <c r="A4" s="37"/>
+      <c r="B4" s="36" t="n">
         <v>40022</v>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="36" t="n">
         <v>30021</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>76</v>
+      <c r="D4" s="36" t="s">
+        <v>55</v>
       </c>
-      <c r="E4" s="37" t="n">
+      <c r="E4" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="37" t="n">
+      <c r="F4" s="36" t="n">
         <v>0.8</v>
       </c>
-      <c r="G4" s="38"/>
+      <c r="G4" s="37"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38"/>
-      <c r="B5" s="39" t="n">
+      <c r="A5" s="37"/>
+      <c r="B5" s="38" t="n">
         <v>40023</v>
       </c>
-      <c r="C5" s="39" t="n">
+      <c r="C5" s="38" t="n">
         <v>30021</v>
       </c>
-      <c r="D5" s="39" t="s">
-        <v>77</v>
+      <c r="D5" s="38" t="s">
+        <v>56</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="38" t="n">
         <v>0.55</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="38" t="n">
         <v>0.8</v>
       </c>
-      <c r="G5" s="38"/>
+      <c r="G5" s="37"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="17" t="n">
@@ -34887,13 +34466,13 @@
       <c r="C6" s="17" t="n">
         <v>30022</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>75</v>
+      <c r="D6" s="35" t="s">
+        <v>54</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="E6" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="F6" s="37" t="n">
+      <c r="F6" s="36" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -34904,13 +34483,13 @@
       <c r="C7" s="17" t="n">
         <v>30022</v>
       </c>
-      <c r="D7" s="37" t="s">
-        <v>76</v>
+      <c r="D7" s="36" t="s">
+        <v>55</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="36" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -34921,30 +34500,30 @@
       <c r="C8" s="17" t="n">
         <v>30022</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>77</v>
+      <c r="D8" s="38" t="s">
+        <v>56</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="38" t="n">
         <v>0.55</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="38" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="38" t="n">
         <v>40027</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>30023</v>
       </c>
-      <c r="D9" s="36" t="s">
-        <v>75</v>
+      <c r="D9" s="35" t="s">
+        <v>54</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="F9" s="37" t="n">
+      <c r="F9" s="36" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -34955,13 +34534,13 @@
       <c r="C10" s="17" t="n">
         <v>30023</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>76</v>
+      <c r="D10" s="36" t="s">
+        <v>55</v>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="36" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -34972,13 +34551,13 @@
       <c r="C11" s="17" t="n">
         <v>30023</v>
       </c>
-      <c r="D11" s="39" t="s">
-        <v>77</v>
+      <c r="D11" s="38" t="s">
+        <v>56</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="38" t="n">
         <v>0.55</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="38" t="n">
         <v>0.8</v>
       </c>
     </row>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="79">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Forward.AM_Roll_Relaxed_Forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward</t>
   </si>
   <si>
     <t xml:space="preserve">Backward</t>
@@ -277,19 +280,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="12"/>
@@ -609,37 +609,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -779,7 +779,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.08"/>
@@ -1115,7 +1115,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="5.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="8.94"/>
@@ -1366,8 +1366,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="7.69140625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr defaultColWidth="7.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.38"/>
@@ -1378,7 +1378,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="17" width="11.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="17" width="10.87"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="17" width="7.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="17" width="7.68"/>
   </cols>
   <sheetData>
     <row r="1" s="20" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1493,13 +1493,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="0" t="n">
         <v>30022</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="0" t="n">
         <v>10021</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="0" t="s">
         <v>48</v>
       </c>
       <c r="E4" s="26" t="s">
@@ -1508,16 +1508,17 @@
       <c r="F4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K4" s="17" t="n">
+      <c r="G4" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="0"/>
+      <c r="I4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="L4" s="12" t="b">
@@ -1526,14 +1527,14 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="17" t="n">
         <v>30023</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="17" t="n">
         <v>10021</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>50</v>
+      <c r="D5" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>37</v>
@@ -1542,15 +1543,15 @@
         <v>39</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K5" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="L5" s="12" t="b">
@@ -1562,11 +1563,11 @@
       <c r="B6" s="17" t="n">
         <v>30024</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="26" t="n">
         <v>10021</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>37</v>
@@ -1575,15 +1576,15 @@
         <v>39</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K6" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="L6" s="12" t="b">
@@ -1595,11 +1596,11 @@
       <c r="B7" s="26" t="n">
         <v>30025</v>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="17" t="n">
         <v>10021</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>37</v>
@@ -1608,15 +1609,15 @@
         <v>39</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="L7" s="12" t="b">
@@ -1628,11 +1629,11 @@
       <c r="B8" s="17" t="n">
         <v>30026</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="26" t="n">
         <v>10021</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>37</v>
@@ -1641,15 +1642,15 @@
         <v>39</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="L8" s="12" t="b">
@@ -1661,11 +1662,11 @@
       <c r="B9" s="26" t="n">
         <v>30027</v>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="17" t="n">
         <v>10021</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>37</v>
@@ -1674,15 +1675,15 @@
         <v>39</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K9" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="L9" s="12" t="b">
@@ -1694,11 +1695,11 @@
       <c r="B10" s="26" t="n">
         <v>30028</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="26" t="n">
         <v>10021</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>37</v>
@@ -1707,15 +1708,15 @@
         <v>39</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K10" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K10" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="L10" s="12" t="b">
@@ -1724,19 +1725,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="0" t="n">
         <v>30029</v>
       </c>
       <c r="C11" s="17" t="n">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="12" t="s">
         <v>39</v>
       </c>
       <c r="G11" s="27" t="s">
@@ -1760,11 +1761,11 @@
       <c r="B12" s="26" t="n">
         <v>30030</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="0" t="n">
         <v>10022</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>48</v>
+      <c r="D12" s="0" t="s">
+        <v>39</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>37</v>
@@ -1775,13 +1776,14 @@
       <c r="G12" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K12" s="12" t="n">
+      <c r="H12" s="0"/>
+      <c r="I12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="L12" s="12" t="b">
@@ -1797,16 +1799,16 @@
         <v>10022</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="27" t="s">
         <v>39</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I13" s="17" t="n">
         <v>1</v>
@@ -1829,8 +1831,8 @@
       <c r="C14" s="17" t="n">
         <v>10022</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>52</v>
+      <c r="D14" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>37</v>
@@ -1839,7 +1841,7 @@
         <v>39</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>1</v>
@@ -1863,7 +1865,7 @@
         <v>10022</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>37</v>
@@ -1872,7 +1874,7 @@
         <v>39</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I15" s="17" t="n">
         <v>1</v>
@@ -1896,7 +1898,7 @@
         <v>10022</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>37</v>
@@ -1905,7 +1907,7 @@
         <v>39</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>1</v>
@@ -1929,7 +1931,7 @@
         <v>10022</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>37</v>
@@ -1938,7 +1940,7 @@
         <v>39</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I17" s="17" t="n">
         <v>1</v>
@@ -1962,7 +1964,7 @@
         <v>10022</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>37</v>
@@ -1971,7 +1973,7 @@
         <v>39</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>1</v>
@@ -1988,9 +1990,70 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="12"/>
+      <c r="B19" s="0" t="n">
+        <v>30037</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>10022</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="12" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="n">
+        <v>30038</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>10022</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L20" s="12" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2008,7 +2071,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="7.703125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="7.51"/>
@@ -2051,19 +2114,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2075,7 +2138,7 @@
         <v>30021</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="33" t="n">
         <v>0.1</v>
@@ -2094,7 +2157,7 @@
         <v>30021</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" s="34" t="n">
         <v>0</v>
@@ -2113,7 +2176,7 @@
         <v>30021</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="36" t="n">
         <v>0.55</v>
@@ -2131,7 +2194,7 @@
         <v>30022</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>0.1</v>
@@ -2148,7 +2211,7 @@
         <v>30022</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>0</v>
@@ -2165,7 +2228,7 @@
         <v>30022</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0.55</v>
@@ -2182,7 +2245,7 @@
         <v>30023</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>0.1</v>
@@ -2199,7 +2262,7 @@
         <v>30023</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>0</v>
@@ -2216,7 +2279,7 @@
         <v>30023</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0.55</v>
@@ -2233,7 +2296,7 @@
         <v>30024</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>0.1</v>
@@ -2250,7 +2313,7 @@
         <v>30024</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>0</v>
@@ -2267,7 +2330,7 @@
         <v>30024</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>0.55</v>
@@ -2284,7 +2347,7 @@
         <v>30025</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" s="33" t="n">
         <v>0.1</v>
@@ -2301,7 +2364,7 @@
         <v>30025</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" s="34" t="n">
         <v>0</v>
@@ -2318,7 +2381,7 @@
         <v>30025</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0.55</v>
@@ -2335,7 +2398,7 @@
         <v>30026</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E18" s="33" t="n">
         <v>0.1</v>
@@ -2352,7 +2415,7 @@
         <v>30026</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E19" s="34" t="n">
         <v>0</v>
@@ -2369,7 +2432,7 @@
         <v>30026</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0.55</v>
@@ -2386,7 +2449,7 @@
         <v>30027</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="33" t="n">
         <v>0.1</v>
@@ -2403,7 +2466,7 @@
         <v>30027</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" s="34" t="n">
         <v>0</v>
@@ -2420,7 +2483,7 @@
         <v>30027</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" s="36" t="n">
         <v>0.55</v>
@@ -2437,7 +2500,7 @@
         <v>30028</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E24" s="33" t="n">
         <v>0.1</v>
@@ -2454,7 +2517,7 @@
         <v>30028</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" s="34" t="n">
         <v>0</v>
@@ -2471,7 +2534,7 @@
         <v>30028</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" s="36" t="n">
         <v>0.55</v>
@@ -2488,7 +2551,7 @@
         <v>30029</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E27" s="33" t="n">
         <v>0.1</v>
@@ -2505,7 +2568,7 @@
         <v>30029</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E28" s="34" t="n">
         <v>0</v>
@@ -2522,7 +2585,7 @@
         <v>30029</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" s="36" t="n">
         <v>0.55</v>
@@ -2539,7 +2602,7 @@
         <v>30030</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30" s="33" t="n">
         <v>0.1</v>
@@ -2556,7 +2619,7 @@
         <v>30030</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E31" s="34" t="n">
         <v>0</v>
@@ -2573,7 +2636,7 @@
         <v>30030</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E32" s="36" t="n">
         <v>0.55</v>
@@ -2590,7 +2653,7 @@
         <v>30031</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E33" s="33" t="n">
         <v>0.1</v>
@@ -2607,7 +2670,7 @@
         <v>30031</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E34" s="34" t="n">
         <v>0</v>
@@ -2624,7 +2687,7 @@
         <v>30031</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E35" s="36" t="n">
         <v>0.55</v>
@@ -2641,7 +2704,7 @@
         <v>30032</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E36" s="33" t="n">
         <v>0.1</v>
@@ -2658,7 +2721,7 @@
         <v>30032</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E37" s="34" t="n">
         <v>0</v>
@@ -2675,7 +2738,7 @@
         <v>30032</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E38" s="36" t="n">
         <v>0.55</v>
@@ -2692,7 +2755,7 @@
         <v>30033</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E39" s="33" t="n">
         <v>0.1</v>
@@ -2709,7 +2772,7 @@
         <v>30033</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E40" s="34" t="n">
         <v>0</v>
@@ -2726,7 +2789,7 @@
         <v>30033</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E41" s="36" t="n">
         <v>0.55</v>
@@ -2743,7 +2806,7 @@
         <v>30034</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E42" s="33" t="n">
         <v>0.1</v>
@@ -2760,7 +2823,7 @@
         <v>30034</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E43" s="34" t="n">
         <v>0</v>
@@ -2777,7 +2840,7 @@
         <v>30034</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E44" s="36" t="n">
         <v>0.55</v>
@@ -2794,7 +2857,7 @@
         <v>30035</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E45" s="33" t="n">
         <v>0.1</v>
@@ -2811,7 +2874,7 @@
         <v>30035</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E46" s="34" t="n">
         <v>0</v>
@@ -2828,7 +2891,7 @@
         <v>30035</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E47" s="36" t="n">
         <v>0.55</v>
@@ -2845,7 +2908,7 @@
         <v>30036</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E48" s="33" t="n">
         <v>0.1</v>
@@ -2862,7 +2925,7 @@
         <v>30036</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E49" s="34" t="n">
         <v>0</v>
@@ -2879,12 +2942,114 @@
         <v>30036</v>
       </c>
       <c r="D50" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" s="36" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F50" s="36" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="17" t="n">
+        <v>40069</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>30037</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F51" s="34" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="17" t="n">
+        <v>40070</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>30037</v>
+      </c>
+      <c r="D52" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="E50" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F50" s="36" t="n">
+      <c r="E52" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="34" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="17" t="n">
+        <v>40071</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>30037</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" s="36" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F53" s="36" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="36" t="n">
+        <v>40072</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>30038</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F54" s="34" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="17" t="n">
+        <v>40073</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>30038</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="34" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="17" t="n">
+        <v>40074</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>30038</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" s="36" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F56" s="36" t="n">
         <v>0.8</v>
       </c>
     </row>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="80">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_BackwardRight.AM_Dodge_Relaxed_BackwardRight</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -326,7 +329,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,7 +345,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFFFF5CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFFFF5CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF5CE"/>
+        <bgColor rgb="FFFFFFD7"/>
       </patternFill>
     </fill>
   </fills>
@@ -380,7 +395,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -481,15 +496,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -558,7 +597,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFFFFD7"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -575,7 +614,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFF5CE"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1366,8 +1405,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultColWidth="7.6875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="14.38"/>
@@ -1457,7 +1496,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25"/>
       <c r="B3" s="25" t="n">
         <v>30021</v>
@@ -1471,588 +1510,591 @@
       <c r="E3" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="27" t="s">
         <v>39</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K3" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L3" s="12" t="b">
+      <c r="H3" s="27"/>
+      <c r="I3" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K3" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L3" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+    <row r="4" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="28" t="n">
         <v>30022</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="28" t="n">
         <v>10021</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="27" t="s">
         <v>39</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="0"/>
-      <c r="I4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L4" s="12" t="b">
+      <c r="I4" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L4" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17" t="n">
+    <row r="5" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="28" t="n">
         <v>30023</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="28" t="n">
         <v>10021</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="27" t="s">
         <v>49</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K5" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L5" s="12" t="b">
+      <c r="I5" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17" t="n">
+    <row r="6" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="n">
         <v>30024</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>10021</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="29" t="s">
         <v>51</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L6" s="12" t="b">
+      <c r="I6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L6" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="26" t="n">
         <v>30025</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="28" t="n">
         <v>10021</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="29" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L7" s="12" t="b">
+      <c r="I7" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17" t="n">
+    <row r="8" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="n">
         <v>30026</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>10021</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="29" t="s">
         <v>55</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L8" s="12" t="b">
+      <c r="I8" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L8" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="26" t="n">
         <v>30027</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="28" t="n">
         <v>10021</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="29" t="s">
         <v>57</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L9" s="12" t="b">
+      <c r="I9" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L9" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="26" t="n">
         <v>30028</v>
       </c>
       <c r="C10" s="26" t="n">
         <v>10021</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="12" t="b">
+      <c r="I10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="n">
+    <row r="11" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="28" t="n">
         <v>30029</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="28" t="n">
         <v>10021</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="29" t="s">
         <v>61</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L11" s="12" t="b">
+      <c r="I11" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K11" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L11" s="27" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="26" t="n">
+    <row r="12" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="31" t="n">
         <v>30030</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="H12" s="0"/>
-      <c r="I12" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L12" s="12" t="b">
+      <c r="I12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L12" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17" t="n">
+    <row r="13" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="30" t="n">
         <v>30031</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L13" s="12" t="b">
+      <c r="I13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="26" t="n">
+    <row r="14" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="31" t="n">
         <v>30032</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L14" s="12" t="b">
+      <c r="I14" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L14" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="17" t="n">
+    <row r="15" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="30" t="n">
         <v>30033</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="I15" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L15" s="12" t="b">
+      <c r="I15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L15" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="26" t="n">
+    <row r="16" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="31" t="n">
         <v>30034</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L16" s="12" t="b">
+      <c r="I16" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K16" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L16" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="17" t="n">
+    <row r="17" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="30" t="n">
         <v>30035</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="12" t="b">
+      <c r="I17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="26" t="n">
+    <row r="18" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="31" t="n">
         <v>30036</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="G18" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L18" s="12" t="b">
+      <c r="I18" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K18" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="n">
+    <row r="19" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="30" t="n">
         <v>30037</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L19" s="12" t="b">
+      <c r="I19" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="n">
+    <row r="20" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="30" t="n">
         <v>30038</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="30" t="n">
         <v>10022</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L20" s="12" t="b">
+      <c r="I20" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K20" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L20" s="32" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2125,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="11.01"/>
   </cols>
   <sheetData>
-    <row r="1" s="29" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2099,92 +2141,92 @@
       <c r="E1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F1" s="28" t="n">
+      <c r="F1" s="34" t="n">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="31" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
+    <row r="2" s="37" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33" t="n">
+      <c r="A3" s="38"/>
+      <c r="B3" s="39" t="n">
         <v>40021</v>
       </c>
-      <c r="C3" s="33" t="n">
+      <c r="C3" s="39" t="n">
         <v>30021</v>
       </c>
-      <c r="D3" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F3" s="34" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G3" s="32"/>
+      <c r="D3" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="40" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35"/>
-      <c r="B4" s="34" t="n">
+      <c r="A4" s="41"/>
+      <c r="B4" s="40" t="n">
         <v>40022</v>
       </c>
-      <c r="C4" s="34" t="n">
+      <c r="C4" s="40" t="n">
         <v>30021</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G4" s="35"/>
+      <c r="D4" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" s="41"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35"/>
-      <c r="B5" s="36" t="n">
+      <c r="A5" s="41"/>
+      <c r="B5" s="42" t="n">
         <v>40023</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="42" t="n">
         <v>30021</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F5" s="36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G5" s="35"/>
+      <c r="D5" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F5" s="42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="17" t="n">
@@ -2193,13 +2235,13 @@
       <c r="C6" s="17" t="n">
         <v>30022</v>
       </c>
-      <c r="D6" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F6" s="34" t="n">
+      <c r="D6" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2210,13 +2252,13 @@
       <c r="C7" s="17" t="n">
         <v>30022</v>
       </c>
-      <c r="D7" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="34" t="n">
+      <c r="D7" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2227,30 +2269,30 @@
       <c r="C8" s="17" t="n">
         <v>30022</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F8" s="36" t="n">
+      <c r="D8" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F8" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="42" t="n">
         <v>40027</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>30023</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="34" t="n">
+      <c r="D9" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2261,13 +2303,13 @@
       <c r="C10" s="17" t="n">
         <v>30023</v>
       </c>
-      <c r="D10" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="34" t="n">
+      <c r="D10" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2278,64 +2320,64 @@
       <c r="C11" s="17" t="n">
         <v>30023</v>
       </c>
-      <c r="D11" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F11" s="36" t="n">
+      <c r="D11" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F11" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="39" t="n">
         <v>40030</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>30024</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F12" s="34" t="n">
+      <c r="D12" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="40" t="n">
         <v>40031</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>30024</v>
       </c>
-      <c r="D13" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="34" t="n">
+      <c r="D13" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="42" t="n">
         <v>40032</v>
       </c>
       <c r="C14" s="17" t="n">
         <v>30024</v>
       </c>
-      <c r="D14" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F14" s="36" t="n">
+      <c r="D14" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F14" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2346,13 +2388,13 @@
       <c r="C15" s="17" t="n">
         <v>30025</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F15" s="34" t="n">
+      <c r="D15" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2363,13 +2405,13 @@
       <c r="C16" s="17" t="n">
         <v>30025</v>
       </c>
-      <c r="D16" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="34" t="n">
+      <c r="D16" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2380,30 +2422,30 @@
       <c r="C17" s="17" t="n">
         <v>30025</v>
       </c>
-      <c r="D17" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F17" s="36" t="n">
+      <c r="D17" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F17" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="36" t="n">
+      <c r="B18" s="42" t="n">
         <v>40036</v>
       </c>
       <c r="C18" s="17" t="n">
         <v>30026</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="34" t="n">
+      <c r="D18" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F18" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2414,13 +2456,13 @@
       <c r="C19" s="17" t="n">
         <v>30026</v>
       </c>
-      <c r="D19" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="34" t="n">
+      <c r="D19" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2431,64 +2473,64 @@
       <c r="C20" s="17" t="n">
         <v>30026</v>
       </c>
-      <c r="D20" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F20" s="36" t="n">
+      <c r="D20" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F20" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="39" t="n">
         <v>40039</v>
       </c>
       <c r="C21" s="17" t="n">
         <v>30027</v>
       </c>
-      <c r="D21" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="34" t="n">
+      <c r="D21" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F21" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="34" t="n">
+      <c r="B22" s="40" t="n">
         <v>40040</v>
       </c>
       <c r="C22" s="17" t="n">
         <v>30027</v>
       </c>
-      <c r="D22" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="34" t="n">
+      <c r="D22" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="42" t="n">
         <v>40041</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>30027</v>
       </c>
-      <c r="D23" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F23" s="36" t="n">
+      <c r="D23" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F23" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2499,13 +2541,13 @@
       <c r="C24" s="17" t="n">
         <v>30028</v>
       </c>
-      <c r="D24" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="34" t="n">
+      <c r="D24" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2516,13 +2558,13 @@
       <c r="C25" s="17" t="n">
         <v>30028</v>
       </c>
-      <c r="D25" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="34" t="n">
+      <c r="D25" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2533,64 +2575,64 @@
       <c r="C26" s="17" t="n">
         <v>30028</v>
       </c>
-      <c r="D26" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F26" s="36" t="n">
+      <c r="D26" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F26" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="33" t="n">
+      <c r="B27" s="39" t="n">
         <v>40045</v>
       </c>
       <c r="C27" s="17" t="n">
         <v>30029</v>
       </c>
-      <c r="D27" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="34" t="n">
+      <c r="D27" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="34" t="n">
+      <c r="B28" s="40" t="n">
         <v>40046</v>
       </c>
       <c r="C28" s="17" t="n">
         <v>30029</v>
       </c>
-      <c r="D28" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="34" t="n">
+      <c r="D28" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="42" t="n">
         <v>40047</v>
       </c>
       <c r="C29" s="17" t="n">
         <v>30029</v>
       </c>
-      <c r="D29" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F29" s="36" t="n">
+      <c r="D29" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F29" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2601,13 +2643,13 @@
       <c r="C30" s="17" t="n">
         <v>30030</v>
       </c>
-      <c r="D30" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F30" s="34" t="n">
+      <c r="D30" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2618,13 +2660,13 @@
       <c r="C31" s="17" t="n">
         <v>30030</v>
       </c>
-      <c r="D31" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="34" t="n">
+      <c r="D31" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2635,30 +2677,30 @@
       <c r="C32" s="17" t="n">
         <v>30030</v>
       </c>
-      <c r="D32" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F32" s="36" t="n">
+      <c r="D32" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F32" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="36" t="n">
+      <c r="B33" s="42" t="n">
         <v>40051</v>
       </c>
       <c r="C33" s="17" t="n">
         <v>30031</v>
       </c>
-      <c r="D33" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F33" s="34" t="n">
+      <c r="D33" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2669,13 +2711,13 @@
       <c r="C34" s="17" t="n">
         <v>30031</v>
       </c>
-      <c r="D34" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="34" t="n">
+      <c r="D34" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2686,64 +2728,64 @@
       <c r="C35" s="17" t="n">
         <v>30031</v>
       </c>
-      <c r="D35" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F35" s="36" t="n">
+      <c r="D35" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F35" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="33" t="n">
+      <c r="B36" s="39" t="n">
         <v>40054</v>
       </c>
       <c r="C36" s="17" t="n">
         <v>30032</v>
       </c>
-      <c r="D36" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F36" s="34" t="n">
+      <c r="D36" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E36" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F36" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="34" t="n">
+      <c r="B37" s="40" t="n">
         <v>40055</v>
       </c>
       <c r="C37" s="17" t="n">
         <v>30032</v>
       </c>
-      <c r="D37" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E37" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="34" t="n">
+      <c r="D37" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="36" t="n">
+      <c r="B38" s="42" t="n">
         <v>40056</v>
       </c>
       <c r="C38" s="17" t="n">
         <v>30032</v>
       </c>
-      <c r="D38" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E38" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F38" s="36" t="n">
+      <c r="D38" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F38" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2754,13 +2796,13 @@
       <c r="C39" s="17" t="n">
         <v>30033</v>
       </c>
-      <c r="D39" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F39" s="34" t="n">
+      <c r="D39" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F39" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2771,13 +2813,13 @@
       <c r="C40" s="17" t="n">
         <v>30033</v>
       </c>
-      <c r="D40" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E40" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="34" t="n">
+      <c r="D40" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2788,30 +2830,30 @@
       <c r="C41" s="17" t="n">
         <v>30033</v>
       </c>
-      <c r="D41" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F41" s="36" t="n">
+      <c r="D41" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F41" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="36" t="n">
+      <c r="B42" s="42" t="n">
         <v>40060</v>
       </c>
       <c r="C42" s="17" t="n">
         <v>30034</v>
       </c>
-      <c r="D42" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F42" s="34" t="n">
+      <c r="D42" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E42" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F42" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2822,13 +2864,13 @@
       <c r="C43" s="17" t="n">
         <v>30034</v>
       </c>
-      <c r="D43" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E43" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="34" t="n">
+      <c r="D43" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2839,64 +2881,64 @@
       <c r="C44" s="17" t="n">
         <v>30034</v>
       </c>
-      <c r="D44" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E44" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F44" s="36" t="n">
+      <c r="D44" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F44" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="33" t="n">
+      <c r="B45" s="39" t="n">
         <v>40063</v>
       </c>
       <c r="C45" s="17" t="n">
         <v>30035</v>
       </c>
-      <c r="D45" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F45" s="34" t="n">
+      <c r="D45" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F45" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="34" t="n">
+      <c r="B46" s="40" t="n">
         <v>40064</v>
       </c>
       <c r="C46" s="17" t="n">
         <v>30035</v>
       </c>
-      <c r="D46" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E46" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="34" t="n">
+      <c r="D46" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E46" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="42" t="n">
         <v>40065</v>
       </c>
       <c r="C47" s="17" t="n">
         <v>30035</v>
       </c>
-      <c r="D47" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E47" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F47" s="36" t="n">
+      <c r="D47" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F47" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2907,13 +2949,13 @@
       <c r="C48" s="17" t="n">
         <v>30036</v>
       </c>
-      <c r="D48" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F48" s="34" t="n">
+      <c r="D48" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F48" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2924,13 +2966,13 @@
       <c r="C49" s="17" t="n">
         <v>30036</v>
       </c>
-      <c r="D49" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="34" t="n">
+      <c r="D49" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E49" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2941,13 +2983,13 @@
       <c r="C50" s="17" t="n">
         <v>30036</v>
       </c>
-      <c r="D50" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E50" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F50" s="36" t="n">
+      <c r="D50" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F50" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2958,13 +3000,13 @@
       <c r="C51" s="17" t="n">
         <v>30037</v>
       </c>
-      <c r="D51" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F51" s="34" t="n">
+      <c r="D51" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F51" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2975,13 +3017,13 @@
       <c r="C52" s="17" t="n">
         <v>30037</v>
       </c>
-      <c r="D52" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="34" t="n">
+      <c r="D52" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2992,30 +3034,30 @@
       <c r="C53" s="17" t="n">
         <v>30037</v>
       </c>
-      <c r="D53" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E53" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F53" s="36" t="n">
+      <c r="D53" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F53" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="36" t="n">
+      <c r="B54" s="42" t="n">
         <v>40072</v>
       </c>
       <c r="C54" s="17" t="n">
         <v>30038</v>
       </c>
-      <c r="D54" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F54" s="34" t="n">
+      <c r="D54" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F54" s="40" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -3026,13 +3068,13 @@
       <c r="C55" s="17" t="n">
         <v>30038</v>
       </c>
-      <c r="D55" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E55" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="34" t="n">
+      <c r="D55" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="40" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -3043,13 +3085,13 @@
       <c r="C56" s="17" t="n">
         <v>30038</v>
       </c>
-      <c r="D56" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E56" s="36" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F56" s="36" t="n">
+      <c r="D56" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="42" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F56" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="85">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -166,6 +166,9 @@
     <t xml:space="preserve">bUseRootMotion</t>
   </si>
   <si>
+    <t xml:space="preserve">NextComboLAnimationTid</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Forward.AM_Roll_Relaxed_Forward</t>
   </si>
   <si>
@@ -238,7 +241,19 @@
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_BackwardRight.AM_Dodge_Relaxed_BackwardRight</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_1.AM_Player_LightAttack_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본공격1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_2.AM_Player_LightAttack_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본공격2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격1</t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -492,7 +507,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1405,7 +1420,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="9.3"/>
@@ -1417,7 +1432,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="17" width="11.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="17" width="10.87"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="17" width="7.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="17" width="17.96"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="14" style="17" width="7.68"/>
   </cols>
   <sheetData>
     <row r="1" s="20" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1457,6 +1473,12 @@
       <c r="L1" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="M1" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="2" s="24" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="21" t="s">
@@ -1494,6 +1516,9 @@
       </c>
       <c r="L2" s="23" t="s">
         <v>46</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1514,7 +1539,7 @@
         <v>39</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3" s="27"/>
       <c r="I3" s="27" t="n">
@@ -1539,7 +1564,7 @@
         <v>10021</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>37</v>
@@ -1548,7 +1573,7 @@
         <v>39</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" s="27" t="n">
         <v>1</v>
@@ -1572,7 +1597,7 @@
         <v>10021</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>37</v>
@@ -1581,7 +1606,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="28" t="n">
         <v>1</v>
@@ -1605,7 +1630,7 @@
         <v>10021</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>37</v>
@@ -1614,7 +1639,7 @@
         <v>39</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>1</v>
@@ -1638,7 +1663,7 @@
         <v>10021</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>37</v>
@@ -1647,7 +1672,7 @@
         <v>39</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I7" s="28" t="n">
         <v>1</v>
@@ -1671,7 +1696,7 @@
         <v>10021</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>37</v>
@@ -1680,7 +1705,7 @@
         <v>39</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>1</v>
@@ -1704,7 +1729,7 @@
         <v>10021</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>37</v>
@@ -1713,7 +1738,7 @@
         <v>39</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I9" s="28" t="n">
         <v>1</v>
@@ -1737,7 +1762,7 @@
         <v>10021</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>37</v>
@@ -1746,7 +1771,7 @@
         <v>39</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>1</v>
@@ -1770,7 +1795,7 @@
         <v>10021</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>37</v>
@@ -1779,7 +1804,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I11" s="28" t="n">
         <v>1</v>
@@ -1812,7 +1837,7 @@
         <v>39</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I12" s="30" t="n">
         <v>1</v>
@@ -1836,7 +1861,7 @@
         <v>10022</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>37</v>
@@ -1845,7 +1870,7 @@
         <v>39</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I13" s="30" t="n">
         <v>1</v>
@@ -1869,7 +1894,7 @@
         <v>10022</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>37</v>
@@ -1878,7 +1903,7 @@
         <v>39</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I14" s="32" t="n">
         <v>1</v>
@@ -1902,7 +1927,7 @@
         <v>10022</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>37</v>
@@ -1911,7 +1936,7 @@
         <v>39</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="30" t="n">
         <v>1</v>
@@ -1935,7 +1960,7 @@
         <v>10022</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>37</v>
@@ -1944,7 +1969,7 @@
         <v>39</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I16" s="32" t="n">
         <v>1</v>
@@ -1968,7 +1993,7 @@
         <v>10022</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="31" t="s">
         <v>37</v>
@@ -1977,7 +2002,7 @@
         <v>39</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I17" s="30" t="n">
         <v>1</v>
@@ -2001,7 +2026,7 @@
         <v>10022</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" s="31" t="s">
         <v>37</v>
@@ -2010,7 +2035,7 @@
         <v>39</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I18" s="32" t="n">
         <v>1</v>
@@ -2034,7 +2059,7 @@
         <v>10022</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" s="31" t="s">
         <v>37</v>
@@ -2043,7 +2068,7 @@
         <v>39</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" s="30" t="n">
         <v>1</v>
@@ -2067,7 +2092,7 @@
         <v>10022</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E20" s="31" t="s">
         <v>37</v>
@@ -2076,7 +2101,7 @@
         <v>39</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20" s="32" t="n">
         <v>1</v>
@@ -2092,9 +2117,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="17" t="n">
+        <v>31001</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>31002</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="17" t="s">
-        <v>71</v>
+      <c r="B22" s="17" t="n">
+        <v>31002</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="17" t="n">
+        <v>32001</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2156,19 +2209,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2180,7 +2233,7 @@
         <v>30021</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E3" s="39" t="n">
         <v>0.1</v>
@@ -2199,7 +2252,7 @@
         <v>30021</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E4" s="40" t="n">
         <v>0</v>
@@ -2218,7 +2271,7 @@
         <v>30021</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E5" s="42" t="n">
         <v>0.55</v>
@@ -2236,7 +2289,7 @@
         <v>30022</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E6" s="39" t="n">
         <v>0.1</v>
@@ -2253,7 +2306,7 @@
         <v>30022</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E7" s="40" t="n">
         <v>0</v>
@@ -2270,7 +2323,7 @@
         <v>30022</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E8" s="42" t="n">
         <v>0.55</v>
@@ -2287,7 +2340,7 @@
         <v>30023</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E9" s="39" t="n">
         <v>0.1</v>
@@ -2304,7 +2357,7 @@
         <v>30023</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E10" s="40" t="n">
         <v>0</v>
@@ -2321,7 +2374,7 @@
         <v>30023</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>0.55</v>
@@ -2338,7 +2391,7 @@
         <v>30024</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E12" s="39" t="n">
         <v>0.1</v>
@@ -2355,7 +2408,7 @@
         <v>30024</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E13" s="40" t="n">
         <v>0</v>
@@ -2372,7 +2425,7 @@
         <v>30024</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>0.55</v>
@@ -2389,7 +2442,7 @@
         <v>30025</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E15" s="39" t="n">
         <v>0.1</v>
@@ -2406,7 +2459,7 @@
         <v>30025</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E16" s="40" t="n">
         <v>0</v>
@@ -2423,7 +2476,7 @@
         <v>30025</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>0.55</v>
@@ -2440,7 +2493,7 @@
         <v>30026</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E18" s="39" t="n">
         <v>0.1</v>
@@ -2457,7 +2510,7 @@
         <v>30026</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E19" s="40" t="n">
         <v>0</v>
@@ -2474,7 +2527,7 @@
         <v>30026</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.55</v>
@@ -2491,7 +2544,7 @@
         <v>30027</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E21" s="39" t="n">
         <v>0.1</v>
@@ -2508,7 +2561,7 @@
         <v>30027</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E22" s="40" t="n">
         <v>0</v>
@@ -2525,7 +2578,7 @@
         <v>30027</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E23" s="42" t="n">
         <v>0.55</v>
@@ -2542,7 +2595,7 @@
         <v>30028</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E24" s="39" t="n">
         <v>0.1</v>
@@ -2559,7 +2612,7 @@
         <v>30028</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E25" s="40" t="n">
         <v>0</v>
@@ -2576,7 +2629,7 @@
         <v>30028</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E26" s="42" t="n">
         <v>0.55</v>
@@ -2593,7 +2646,7 @@
         <v>30029</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E27" s="39" t="n">
         <v>0.1</v>
@@ -2610,7 +2663,7 @@
         <v>30029</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E28" s="40" t="n">
         <v>0</v>
@@ -2627,7 +2680,7 @@
         <v>30029</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E29" s="42" t="n">
         <v>0.55</v>
@@ -2644,7 +2697,7 @@
         <v>30030</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E30" s="39" t="n">
         <v>0.1</v>
@@ -2661,7 +2714,7 @@
         <v>30030</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E31" s="40" t="n">
         <v>0</v>
@@ -2678,7 +2731,7 @@
         <v>30030</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E32" s="42" t="n">
         <v>0.55</v>
@@ -2695,7 +2748,7 @@
         <v>30031</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E33" s="39" t="n">
         <v>0.1</v>
@@ -2712,7 +2765,7 @@
         <v>30031</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E34" s="40" t="n">
         <v>0</v>
@@ -2729,7 +2782,7 @@
         <v>30031</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E35" s="42" t="n">
         <v>0.55</v>
@@ -2746,7 +2799,7 @@
         <v>30032</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E36" s="39" t="n">
         <v>0.1</v>
@@ -2763,7 +2816,7 @@
         <v>30032</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E37" s="40" t="n">
         <v>0</v>
@@ -2780,7 +2833,7 @@
         <v>30032</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E38" s="42" t="n">
         <v>0.55</v>
@@ -2797,7 +2850,7 @@
         <v>30033</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E39" s="39" t="n">
         <v>0.1</v>
@@ -2814,7 +2867,7 @@
         <v>30033</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E40" s="40" t="n">
         <v>0</v>
@@ -2831,7 +2884,7 @@
         <v>30033</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E41" s="42" t="n">
         <v>0.55</v>
@@ -2848,7 +2901,7 @@
         <v>30034</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E42" s="39" t="n">
         <v>0.1</v>
@@ -2865,7 +2918,7 @@
         <v>30034</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E43" s="40" t="n">
         <v>0</v>
@@ -2882,7 +2935,7 @@
         <v>30034</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E44" s="42" t="n">
         <v>0.55</v>
@@ -2899,7 +2952,7 @@
         <v>30035</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E45" s="39" t="n">
         <v>0.1</v>
@@ -2916,7 +2969,7 @@
         <v>30035</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E46" s="40" t="n">
         <v>0</v>
@@ -2933,7 +2986,7 @@
         <v>30035</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E47" s="42" t="n">
         <v>0.55</v>
@@ -2950,7 +3003,7 @@
         <v>30036</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E48" s="39" t="n">
         <v>0.1</v>
@@ -2967,7 +3020,7 @@
         <v>30036</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E49" s="40" t="n">
         <v>0</v>
@@ -2984,7 +3037,7 @@
         <v>30036</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E50" s="42" t="n">
         <v>0.55</v>
@@ -3001,7 +3054,7 @@
         <v>30037</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E51" s="39" t="n">
         <v>0.1</v>
@@ -3018,7 +3071,7 @@
         <v>30037</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E52" s="40" t="n">
         <v>0</v>
@@ -3035,7 +3088,7 @@
         <v>30037</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E53" s="42" t="n">
         <v>0.55</v>
@@ -3052,7 +3105,7 @@
         <v>30038</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E54" s="39" t="n">
         <v>0.1</v>
@@ -3069,7 +3122,7 @@
         <v>30038</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E55" s="40" t="n">
         <v>0</v>
@@ -3086,7 +3139,7 @@
         <v>30038</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E56" s="42" t="n">
         <v>0.55</v>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="88">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -253,7 +253,16 @@
     <t xml:space="preserve">기본공격2</t>
   </si>
   <si>
-    <t xml:space="preserve">강공격1</t>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_3.AM_Player_LightAttack_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본공격3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_4.AM_Player_LightAttack_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본공격4</t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -1420,7 +1429,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="9.3"/>
@@ -2138,16 +2147,41 @@
       <c r="G22" s="17" t="s">
         <v>74</v>
       </c>
+      <c r="M22" s="17" t="n">
+        <v>31003</v>
+      </c>
       <c r="N22" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="0" t="n">
+        <v>31003</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>31004</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="n">
+        <v>31004</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="17" t="n">
         <v>32001</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2209,19 +2243,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2233,7 +2267,7 @@
         <v>30021</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E3" s="39" t="n">
         <v>0.1</v>
@@ -2252,7 +2286,7 @@
         <v>30021</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E4" s="40" t="n">
         <v>0</v>
@@ -2271,7 +2305,7 @@
         <v>30021</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E5" s="42" t="n">
         <v>0.55</v>
@@ -2289,7 +2323,7 @@
         <v>30022</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E6" s="39" t="n">
         <v>0.1</v>
@@ -2306,7 +2340,7 @@
         <v>30022</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E7" s="40" t="n">
         <v>0</v>
@@ -2323,7 +2357,7 @@
         <v>30022</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E8" s="42" t="n">
         <v>0.55</v>
@@ -2340,7 +2374,7 @@
         <v>30023</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E9" s="39" t="n">
         <v>0.1</v>
@@ -2357,7 +2391,7 @@
         <v>30023</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E10" s="40" t="n">
         <v>0</v>
@@ -2374,7 +2408,7 @@
         <v>30023</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>0.55</v>
@@ -2391,7 +2425,7 @@
         <v>30024</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E12" s="39" t="n">
         <v>0.1</v>
@@ -2408,7 +2442,7 @@
         <v>30024</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E13" s="40" t="n">
         <v>0</v>
@@ -2425,7 +2459,7 @@
         <v>30024</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>0.55</v>
@@ -2442,7 +2476,7 @@
         <v>30025</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E15" s="39" t="n">
         <v>0.1</v>
@@ -2459,7 +2493,7 @@
         <v>30025</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E16" s="40" t="n">
         <v>0</v>
@@ -2476,7 +2510,7 @@
         <v>30025</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>0.55</v>
@@ -2493,7 +2527,7 @@
         <v>30026</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E18" s="39" t="n">
         <v>0.1</v>
@@ -2510,7 +2544,7 @@
         <v>30026</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E19" s="40" t="n">
         <v>0</v>
@@ -2527,7 +2561,7 @@
         <v>30026</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.55</v>
@@ -2544,7 +2578,7 @@
         <v>30027</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E21" s="39" t="n">
         <v>0.1</v>
@@ -2561,7 +2595,7 @@
         <v>30027</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E22" s="40" t="n">
         <v>0</v>
@@ -2578,7 +2612,7 @@
         <v>30027</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E23" s="42" t="n">
         <v>0.55</v>
@@ -2595,7 +2629,7 @@
         <v>30028</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E24" s="39" t="n">
         <v>0.1</v>
@@ -2612,7 +2646,7 @@
         <v>30028</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E25" s="40" t="n">
         <v>0</v>
@@ -2629,7 +2663,7 @@
         <v>30028</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E26" s="42" t="n">
         <v>0.55</v>
@@ -2646,7 +2680,7 @@
         <v>30029</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E27" s="39" t="n">
         <v>0.1</v>
@@ -2663,7 +2697,7 @@
         <v>30029</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E28" s="40" t="n">
         <v>0</v>
@@ -2680,7 +2714,7 @@
         <v>30029</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E29" s="42" t="n">
         <v>0.55</v>
@@ -2697,7 +2731,7 @@
         <v>30030</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E30" s="39" t="n">
         <v>0.1</v>
@@ -2714,7 +2748,7 @@
         <v>30030</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E31" s="40" t="n">
         <v>0</v>
@@ -2731,7 +2765,7 @@
         <v>30030</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E32" s="42" t="n">
         <v>0.55</v>
@@ -2748,7 +2782,7 @@
         <v>30031</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E33" s="39" t="n">
         <v>0.1</v>
@@ -2765,7 +2799,7 @@
         <v>30031</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E34" s="40" t="n">
         <v>0</v>
@@ -2782,7 +2816,7 @@
         <v>30031</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E35" s="42" t="n">
         <v>0.55</v>
@@ -2799,7 +2833,7 @@
         <v>30032</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E36" s="39" t="n">
         <v>0.1</v>
@@ -2816,7 +2850,7 @@
         <v>30032</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E37" s="40" t="n">
         <v>0</v>
@@ -2833,7 +2867,7 @@
         <v>30032</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E38" s="42" t="n">
         <v>0.55</v>
@@ -2850,7 +2884,7 @@
         <v>30033</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E39" s="39" t="n">
         <v>0.1</v>
@@ -2867,7 +2901,7 @@
         <v>30033</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E40" s="40" t="n">
         <v>0</v>
@@ -2884,7 +2918,7 @@
         <v>30033</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E41" s="42" t="n">
         <v>0.55</v>
@@ -2901,7 +2935,7 @@
         <v>30034</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E42" s="39" t="n">
         <v>0.1</v>
@@ -2918,7 +2952,7 @@
         <v>30034</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E43" s="40" t="n">
         <v>0</v>
@@ -2935,7 +2969,7 @@
         <v>30034</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E44" s="42" t="n">
         <v>0.55</v>
@@ -2952,7 +2986,7 @@
         <v>30035</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E45" s="39" t="n">
         <v>0.1</v>
@@ -2969,7 +3003,7 @@
         <v>30035</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E46" s="40" t="n">
         <v>0</v>
@@ -2986,7 +3020,7 @@
         <v>30035</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E47" s="42" t="n">
         <v>0.55</v>
@@ -3003,7 +3037,7 @@
         <v>30036</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E48" s="39" t="n">
         <v>0.1</v>
@@ -3020,7 +3054,7 @@
         <v>30036</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E49" s="40" t="n">
         <v>0</v>
@@ -3037,7 +3071,7 @@
         <v>30036</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E50" s="42" t="n">
         <v>0.55</v>
@@ -3054,7 +3088,7 @@
         <v>30037</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E51" s="39" t="n">
         <v>0.1</v>
@@ -3071,7 +3105,7 @@
         <v>30037</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E52" s="40" t="n">
         <v>0</v>
@@ -3088,7 +3122,7 @@
         <v>30037</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E53" s="42" t="n">
         <v>0.55</v>
@@ -3105,7 +3139,7 @@
         <v>30038</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E54" s="39" t="n">
         <v>0.1</v>
@@ -3122,7 +3156,7 @@
         <v>30038</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E55" s="40" t="n">
         <v>0</v>
@@ -3139,7 +3173,7 @@
         <v>30038</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E56" s="42" t="n">
         <v>0.55</v>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="91">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -169,6 +169,9 @@
     <t xml:space="preserve">NextComboLAnimationTid</t>
   </si>
   <si>
+    <t xml:space="preserve">NextComboRAnimationTid</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Forward.AM_Roll_Relaxed_Forward</t>
   </si>
   <si>
@@ -263,6 +266,12 @@
   </si>
   <si>
     <t xml:space="preserve">기본공격4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_1.AM_Player_HeavyAttack_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격1</t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -1429,7 +1438,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="9.3"/>
@@ -1488,6 +1497,9 @@
       <c r="N1" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="O1" s="20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" s="24" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="21" t="s">
@@ -1528,6 +1540,9 @@
       </c>
       <c r="M2" s="24" t="s">
         <v>47</v>
+      </c>
+      <c r="O2" s="24" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1548,7 +1563,7 @@
         <v>39</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="27"/>
       <c r="I3" s="27" t="n">
@@ -1573,7 +1588,7 @@
         <v>10021</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>37</v>
@@ -1582,7 +1597,7 @@
         <v>39</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I4" s="27" t="n">
         <v>1</v>
@@ -1606,7 +1621,7 @@
         <v>10021</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>37</v>
@@ -1615,7 +1630,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="28" t="n">
         <v>1</v>
@@ -1639,7 +1654,7 @@
         <v>10021</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>37</v>
@@ -1648,7 +1663,7 @@
         <v>39</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" s="27" t="n">
         <v>1</v>
@@ -1672,7 +1687,7 @@
         <v>10021</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>37</v>
@@ -1681,7 +1696,7 @@
         <v>39</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I7" s="28" t="n">
         <v>1</v>
@@ -1705,7 +1720,7 @@
         <v>10021</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>37</v>
@@ -1714,7 +1729,7 @@
         <v>39</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>1</v>
@@ -1738,7 +1753,7 @@
         <v>10021</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>37</v>
@@ -1747,7 +1762,7 @@
         <v>39</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I9" s="28" t="n">
         <v>1</v>
@@ -1771,7 +1786,7 @@
         <v>10021</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>37</v>
@@ -1780,7 +1795,7 @@
         <v>39</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>1</v>
@@ -1804,7 +1819,7 @@
         <v>10021</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>37</v>
@@ -1813,7 +1828,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I11" s="28" t="n">
         <v>1</v>
@@ -1846,7 +1861,7 @@
         <v>39</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I12" s="30" t="n">
         <v>1</v>
@@ -1870,7 +1885,7 @@
         <v>10022</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>37</v>
@@ -1879,7 +1894,7 @@
         <v>39</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I13" s="30" t="n">
         <v>1</v>
@@ -1903,7 +1918,7 @@
         <v>10022</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>37</v>
@@ -1912,7 +1927,7 @@
         <v>39</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="32" t="n">
         <v>1</v>
@@ -1936,7 +1951,7 @@
         <v>10022</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>37</v>
@@ -1945,7 +1960,7 @@
         <v>39</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I15" s="30" t="n">
         <v>1</v>
@@ -1969,7 +1984,7 @@
         <v>10022</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>37</v>
@@ -1978,7 +1993,7 @@
         <v>39</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I16" s="32" t="n">
         <v>1</v>
@@ -2002,7 +2017,7 @@
         <v>10022</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="31" t="s">
         <v>37</v>
@@ -2011,7 +2026,7 @@
         <v>39</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I17" s="30" t="n">
         <v>1</v>
@@ -2035,7 +2050,7 @@
         <v>10022</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" s="31" t="s">
         <v>37</v>
@@ -2044,7 +2059,7 @@
         <v>39</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I18" s="32" t="n">
         <v>1</v>
@@ -2068,7 +2083,7 @@
         <v>10022</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" s="31" t="s">
         <v>37</v>
@@ -2077,7 +2092,7 @@
         <v>39</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="30" t="n">
         <v>1</v>
@@ -2101,7 +2116,7 @@
         <v>10022</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="31" t="s">
         <v>37</v>
@@ -2110,7 +2125,7 @@
         <v>39</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I20" s="32" t="n">
         <v>1</v>
@@ -2131,13 +2146,13 @@
         <v>31001</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M21" s="17" t="n">
         <v>31002</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,13 +2160,13 @@
         <v>31002</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M22" s="17" t="n">
         <v>31003</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2159,13 +2174,13 @@
         <v>31003</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M23" s="17" t="n">
         <v>31004</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,15 +2188,21 @@
         <v>31004</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="17" t="n">
         <v>32001</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2243,19 +2264,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2267,7 +2288,7 @@
         <v>30021</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E3" s="39" t="n">
         <v>0.1</v>
@@ -2286,7 +2307,7 @@
         <v>30021</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E4" s="40" t="n">
         <v>0</v>
@@ -2305,7 +2326,7 @@
         <v>30021</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E5" s="42" t="n">
         <v>0.55</v>
@@ -2323,7 +2344,7 @@
         <v>30022</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E6" s="39" t="n">
         <v>0.1</v>
@@ -2340,7 +2361,7 @@
         <v>30022</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E7" s="40" t="n">
         <v>0</v>
@@ -2357,7 +2378,7 @@
         <v>30022</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E8" s="42" t="n">
         <v>0.55</v>
@@ -2374,7 +2395,7 @@
         <v>30023</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E9" s="39" t="n">
         <v>0.1</v>
@@ -2391,7 +2412,7 @@
         <v>30023</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E10" s="40" t="n">
         <v>0</v>
@@ -2408,7 +2429,7 @@
         <v>30023</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>0.55</v>
@@ -2425,7 +2446,7 @@
         <v>30024</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E12" s="39" t="n">
         <v>0.1</v>
@@ -2442,7 +2463,7 @@
         <v>30024</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E13" s="40" t="n">
         <v>0</v>
@@ -2459,7 +2480,7 @@
         <v>30024</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>0.55</v>
@@ -2476,7 +2497,7 @@
         <v>30025</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E15" s="39" t="n">
         <v>0.1</v>
@@ -2493,7 +2514,7 @@
         <v>30025</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E16" s="40" t="n">
         <v>0</v>
@@ -2510,7 +2531,7 @@
         <v>30025</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>0.55</v>
@@ -2527,7 +2548,7 @@
         <v>30026</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E18" s="39" t="n">
         <v>0.1</v>
@@ -2544,7 +2565,7 @@
         <v>30026</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E19" s="40" t="n">
         <v>0</v>
@@ -2561,7 +2582,7 @@
         <v>30026</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.55</v>
@@ -2578,7 +2599,7 @@
         <v>30027</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E21" s="39" t="n">
         <v>0.1</v>
@@ -2595,7 +2616,7 @@
         <v>30027</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E22" s="40" t="n">
         <v>0</v>
@@ -2612,7 +2633,7 @@
         <v>30027</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E23" s="42" t="n">
         <v>0.55</v>
@@ -2629,7 +2650,7 @@
         <v>30028</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E24" s="39" t="n">
         <v>0.1</v>
@@ -2646,7 +2667,7 @@
         <v>30028</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E25" s="40" t="n">
         <v>0</v>
@@ -2663,7 +2684,7 @@
         <v>30028</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E26" s="42" t="n">
         <v>0.55</v>
@@ -2680,7 +2701,7 @@
         <v>30029</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E27" s="39" t="n">
         <v>0.1</v>
@@ -2697,7 +2718,7 @@
         <v>30029</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E28" s="40" t="n">
         <v>0</v>
@@ -2714,7 +2735,7 @@
         <v>30029</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E29" s="42" t="n">
         <v>0.55</v>
@@ -2731,7 +2752,7 @@
         <v>30030</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E30" s="39" t="n">
         <v>0.1</v>
@@ -2748,7 +2769,7 @@
         <v>30030</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E31" s="40" t="n">
         <v>0</v>
@@ -2765,7 +2786,7 @@
         <v>30030</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E32" s="42" t="n">
         <v>0.55</v>
@@ -2782,7 +2803,7 @@
         <v>30031</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E33" s="39" t="n">
         <v>0.1</v>
@@ -2799,7 +2820,7 @@
         <v>30031</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E34" s="40" t="n">
         <v>0</v>
@@ -2816,7 +2837,7 @@
         <v>30031</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E35" s="42" t="n">
         <v>0.55</v>
@@ -2833,7 +2854,7 @@
         <v>30032</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E36" s="39" t="n">
         <v>0.1</v>
@@ -2850,7 +2871,7 @@
         <v>30032</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E37" s="40" t="n">
         <v>0</v>
@@ -2867,7 +2888,7 @@
         <v>30032</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E38" s="42" t="n">
         <v>0.55</v>
@@ -2884,7 +2905,7 @@
         <v>30033</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E39" s="39" t="n">
         <v>0.1</v>
@@ -2901,7 +2922,7 @@
         <v>30033</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E40" s="40" t="n">
         <v>0</v>
@@ -2918,7 +2939,7 @@
         <v>30033</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E41" s="42" t="n">
         <v>0.55</v>
@@ -2935,7 +2956,7 @@
         <v>30034</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E42" s="39" t="n">
         <v>0.1</v>
@@ -2952,7 +2973,7 @@
         <v>30034</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E43" s="40" t="n">
         <v>0</v>
@@ -2969,7 +2990,7 @@
         <v>30034</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E44" s="42" t="n">
         <v>0.55</v>
@@ -2986,7 +3007,7 @@
         <v>30035</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E45" s="39" t="n">
         <v>0.1</v>
@@ -3003,7 +3024,7 @@
         <v>30035</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E46" s="40" t="n">
         <v>0</v>
@@ -3020,7 +3041,7 @@
         <v>30035</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E47" s="42" t="n">
         <v>0.55</v>
@@ -3037,7 +3058,7 @@
         <v>30036</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E48" s="39" t="n">
         <v>0.1</v>
@@ -3054,7 +3075,7 @@
         <v>30036</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E49" s="40" t="n">
         <v>0</v>
@@ -3071,7 +3092,7 @@
         <v>30036</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E50" s="42" t="n">
         <v>0.55</v>
@@ -3088,7 +3109,7 @@
         <v>30037</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E51" s="39" t="n">
         <v>0.1</v>
@@ -3105,7 +3126,7 @@
         <v>30037</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E52" s="40" t="n">
         <v>0</v>
@@ -3122,7 +3143,7 @@
         <v>30037</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E53" s="42" t="n">
         <v>0.55</v>
@@ -3139,7 +3160,7 @@
         <v>30038</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E54" s="39" t="n">
         <v>0.1</v>
@@ -3156,7 +3177,7 @@
         <v>30038</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E55" s="40" t="n">
         <v>0</v>
@@ -3173,7 +3194,7 @@
         <v>30038</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E56" s="42" t="n">
         <v>0.55</v>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="93">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t xml:space="preserve">강공격1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_2.AM_Player_HeavyAttack_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">날라서회전베기를조집니다</t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -1438,7 +1444,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="9.3"/>
@@ -2168,6 +2174,9 @@
       <c r="N22" s="17" t="s">
         <v>76</v>
       </c>
+      <c r="O22" s="17" t="n">
+        <v>32002</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="n">
@@ -2203,6 +2212,17 @@
       </c>
       <c r="N25" s="17" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="17" t="n">
+        <v>32002</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2264,19 +2284,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2288,7 +2308,7 @@
         <v>30021</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" s="39" t="n">
         <v>0.1</v>
@@ -2307,7 +2327,7 @@
         <v>30021</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" s="40" t="n">
         <v>0</v>
@@ -2326,7 +2346,7 @@
         <v>30021</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" s="42" t="n">
         <v>0.55</v>
@@ -2344,7 +2364,7 @@
         <v>30022</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" s="39" t="n">
         <v>0.1</v>
@@ -2361,7 +2381,7 @@
         <v>30022</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" s="40" t="n">
         <v>0</v>
@@ -2378,7 +2398,7 @@
         <v>30022</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" s="42" t="n">
         <v>0.55</v>
@@ -2395,7 +2415,7 @@
         <v>30023</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" s="39" t="n">
         <v>0.1</v>
@@ -2412,7 +2432,7 @@
         <v>30023</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" s="40" t="n">
         <v>0</v>
@@ -2429,7 +2449,7 @@
         <v>30023</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>0.55</v>
@@ -2446,7 +2466,7 @@
         <v>30024</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E12" s="39" t="n">
         <v>0.1</v>
@@ -2463,7 +2483,7 @@
         <v>30024</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E13" s="40" t="n">
         <v>0</v>
@@ -2480,7 +2500,7 @@
         <v>30024</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>0.55</v>
@@ -2497,7 +2517,7 @@
         <v>30025</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E15" s="39" t="n">
         <v>0.1</v>
@@ -2514,7 +2534,7 @@
         <v>30025</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E16" s="40" t="n">
         <v>0</v>
@@ -2531,7 +2551,7 @@
         <v>30025</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>0.55</v>
@@ -2548,7 +2568,7 @@
         <v>30026</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" s="39" t="n">
         <v>0.1</v>
@@ -2565,7 +2585,7 @@
         <v>30026</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E19" s="40" t="n">
         <v>0</v>
@@ -2582,7 +2602,7 @@
         <v>30026</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.55</v>
@@ -2599,7 +2619,7 @@
         <v>30027</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E21" s="39" t="n">
         <v>0.1</v>
@@ -2616,7 +2636,7 @@
         <v>30027</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E22" s="40" t="n">
         <v>0</v>
@@ -2633,7 +2653,7 @@
         <v>30027</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E23" s="42" t="n">
         <v>0.55</v>
@@ -2650,7 +2670,7 @@
         <v>30028</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E24" s="39" t="n">
         <v>0.1</v>
@@ -2667,7 +2687,7 @@
         <v>30028</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E25" s="40" t="n">
         <v>0</v>
@@ -2684,7 +2704,7 @@
         <v>30028</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E26" s="42" t="n">
         <v>0.55</v>
@@ -2701,7 +2721,7 @@
         <v>30029</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E27" s="39" t="n">
         <v>0.1</v>
@@ -2718,7 +2738,7 @@
         <v>30029</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E28" s="40" t="n">
         <v>0</v>
@@ -2735,7 +2755,7 @@
         <v>30029</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E29" s="42" t="n">
         <v>0.55</v>
@@ -2752,7 +2772,7 @@
         <v>30030</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E30" s="39" t="n">
         <v>0.1</v>
@@ -2769,7 +2789,7 @@
         <v>30030</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E31" s="40" t="n">
         <v>0</v>
@@ -2786,7 +2806,7 @@
         <v>30030</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E32" s="42" t="n">
         <v>0.55</v>
@@ -2803,7 +2823,7 @@
         <v>30031</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E33" s="39" t="n">
         <v>0.1</v>
@@ -2820,7 +2840,7 @@
         <v>30031</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E34" s="40" t="n">
         <v>0</v>
@@ -2837,7 +2857,7 @@
         <v>30031</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E35" s="42" t="n">
         <v>0.55</v>
@@ -2854,7 +2874,7 @@
         <v>30032</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E36" s="39" t="n">
         <v>0.1</v>
@@ -2871,7 +2891,7 @@
         <v>30032</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E37" s="40" t="n">
         <v>0</v>
@@ -2888,7 +2908,7 @@
         <v>30032</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E38" s="42" t="n">
         <v>0.55</v>
@@ -2905,7 +2925,7 @@
         <v>30033</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E39" s="39" t="n">
         <v>0.1</v>
@@ -2922,7 +2942,7 @@
         <v>30033</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E40" s="40" t="n">
         <v>0</v>
@@ -2939,7 +2959,7 @@
         <v>30033</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E41" s="42" t="n">
         <v>0.55</v>
@@ -2956,7 +2976,7 @@
         <v>30034</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E42" s="39" t="n">
         <v>0.1</v>
@@ -2973,7 +2993,7 @@
         <v>30034</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E43" s="40" t="n">
         <v>0</v>
@@ -2990,7 +3010,7 @@
         <v>30034</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E44" s="42" t="n">
         <v>0.55</v>
@@ -3007,7 +3027,7 @@
         <v>30035</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E45" s="39" t="n">
         <v>0.1</v>
@@ -3024,7 +3044,7 @@
         <v>30035</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E46" s="40" t="n">
         <v>0</v>
@@ -3041,7 +3061,7 @@
         <v>30035</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E47" s="42" t="n">
         <v>0.55</v>
@@ -3058,7 +3078,7 @@
         <v>30036</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E48" s="39" t="n">
         <v>0.1</v>
@@ -3075,7 +3095,7 @@
         <v>30036</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E49" s="40" t="n">
         <v>0</v>
@@ -3092,7 +3112,7 @@
         <v>30036</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E50" s="42" t="n">
         <v>0.55</v>
@@ -3109,7 +3129,7 @@
         <v>30037</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E51" s="39" t="n">
         <v>0.1</v>
@@ -3126,7 +3146,7 @@
         <v>30037</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E52" s="40" t="n">
         <v>0</v>
@@ -3143,7 +3163,7 @@
         <v>30037</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E53" s="42" t="n">
         <v>0.55</v>
@@ -3160,7 +3180,7 @@
         <v>30038</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E54" s="39" t="n">
         <v>0.1</v>
@@ -3177,7 +3197,7 @@
         <v>30038</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E55" s="40" t="n">
         <v>0</v>
@@ -3194,7 +3214,7 @@
         <v>30038</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E56" s="42" t="n">
         <v>0.55</v>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -658,7 +658,7 @@
       <c r="F1" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="G1" t="n">
+      <c r="G1" s="56" t="n">
         <v>1</v>
       </c>
       <c r="H1" s="42" t="n">
@@ -717,7 +717,7 @@
           <t>StaminaCostType</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="56" t="inlineStr">
         <is>
           <t>StaminaRecoveryRateMultiplier</t>
         </is>
@@ -786,7 +786,7 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="56" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="48" t="n">
@@ -829,7 +829,7 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="56" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="48" t="n">
@@ -872,7 +872,7 @@
           <t>OnDemand</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="56" t="n">
         <v>0.5</v>
       </c>
       <c r="H5" s="48" t="n">
@@ -915,7 +915,7 @@
           <t>PerSecond</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="56" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="48" t="n">
@@ -958,7 +958,7 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="56" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="48" t="n">
@@ -1008,7 +1008,7 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="56" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="40" t="n">
@@ -2435,10 +2435,14 @@
       </c>
       <c r="G27" s="64" t="inlineStr">
         <is>
-          <t>/Game/Character/Player/Animation/Montages/Guard/AM_Player_Guard_Loop.AM_Player_Guard_Loop</t>
+          <t>/Game/Character/Player/Animation/Montages/Guard/AM_Player_Guard.AM_Player_Guard</t>
         </is>
       </c>
-      <c r="H27" s="64" t="n"/>
+      <c r="H27" s="64" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
       <c r="I27" s="64" t="n">
         <v>1</v>
       </c>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G5" s="59" t="inlineStr">
         <is>
-          <t>/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Roll_Relaxed_Backward.AM_Roll_Relaxed_Backward</t>
+          <t>/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Player_Dodge_Backstep.AM_Player_Dodge_Backstep</t>
         </is>
       </c>
       <c r="H5" s="51" t="n"/>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G14" s="61" t="inlineStr">
         <is>
-          <t>/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Dodge_Relaxed_Backward.AM_Dodge_Relaxed_Backward</t>
+          <t>/Game/Character/Player/Animation/Montages/DodgeRoll/AM_Player_Dodge_Backstep.AM_Player_Dodge_Backstep</t>
         </is>
       </c>
       <c r="H14" s="52" t="n"/>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -338,16 +338,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="12"/>
@@ -474,147 +477,147 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -698,37 +701,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -868,7 +871,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.08"/>
@@ -1222,7 +1225,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="8.94"/>
@@ -1474,7 +1477,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R1021"/>
-  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="14.38"/>
@@ -4273,18 +4276,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="6.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="23.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="96.38"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="2.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="32" width="8.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="8.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="8.94"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="32" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="7.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="27.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="121.8"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="32" width="2.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="10.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="10.31"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="32" width="12.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4300,16 +4304,17 @@
       <c r="D1" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E1" s="33" t="n">
+      <c r="E1" s="33"/>
+      <c r="F1" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F1" s="33" t="n">
-        <v>1</v>
-      </c>
       <c r="G1" s="33" t="n">
         <v>1</v>
       </c>
       <c r="H1" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4327,13 +4332,14 @@
         <v>43</v>
       </c>
       <c r="E2" s="34"/>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="34"/>
+      <c r="G2" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="H2" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="I2" s="35" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4348,14 +4354,15 @@
       <c r="D3" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36" t="n">
+      <c r="G3" s="36"/>
+      <c r="H3" s="36" t="n">
         <v>71002</v>
       </c>
-      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36"/>
@@ -4368,14 +4375,15 @@
       <c r="D4" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="36"/>
+      <c r="F4" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36" t="n">
+      <c r="G4" s="36"/>
+      <c r="H4" s="36" t="n">
         <v>71003</v>
       </c>
-      <c r="H4" s="36" t="n">
+      <c r="I4" s="36" t="n">
         <v>72002</v>
       </c>
     </row>
@@ -4390,14 +4398,15 @@
       <c r="D5" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="36"/>
+      <c r="F5" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36" t="n">
+      <c r="G5" s="36"/>
+      <c r="H5" s="36" t="n">
         <v>71004</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="36"/>
@@ -4410,12 +4419,13 @@
       <c r="D6" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="36"/>
@@ -4428,12 +4438,13 @@
       <c r="D7" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="36"/>
+      <c r="F7" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="36"/>
       <c r="G7" s="36"/>
       <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
@@ -4446,12 +4457,13 @@
       <c r="D8" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="36"/>
+      <c r="F8" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="36"/>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="103">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -281,6 +281,9 @@
     <t xml:space="preserve">NextOnR</t>
   </si>
   <si>
+    <t xml:space="preserve">DamageCoefficient</t>
+  </si>
+  <si>
     <t xml:space="preserve">기본공격1</t>
   </si>
   <si>
@@ -311,13 +314,25 @@
     <t xml:space="preserve">강공격1</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_Charge.AM_Player_HeavyAttack_Charge</t>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_1.AM_Player_HeavyAttack_1</t>
   </si>
   <si>
     <t xml:space="preserve">날라서회전베기를조집니다</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_2.AM_Player_HeavyAttack_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격 1 – 느린 버전</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_1_Slowed.AM_Player_HeavyAttack_1_Slowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차징공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_ChargeAttack.AM_Player_ChargeAttack</t>
   </si>
 </sst>
 </file>
@@ -4276,22 +4291,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="7.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="27.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="121.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="126.57"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="12.8"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="32" width="2.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="9.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="10.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="10.31"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="32" width="12.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="32" width="20.09"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="32" width="12.8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -4317,8 +4333,11 @@
       <c r="I1" s="33" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J1" s="33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
@@ -4342,42 +4361,46 @@
       <c r="I2" s="35" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J2" s="35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="36"/>
       <c r="B3" s="36" t="n">
         <v>71001</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" s="36"/>
       <c r="F3" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" s="36"/>
       <c r="H3" s="36" t="n">
         <v>71002</v>
       </c>
       <c r="I3" s="36"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J3" s="36"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36"/>
       <c r="B4" s="36" t="n">
         <v>71002</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" s="36"/>
       <c r="F4" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" s="36"/>
       <c r="H4" s="36" t="n">
@@ -4386,84 +4409,133 @@
       <c r="I4" s="36" t="n">
         <v>72002</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J4" s="36"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="36"/>
       <c r="B5" s="36" t="n">
         <v>71003</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E5" s="36"/>
       <c r="F5" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" s="36"/>
       <c r="H5" s="36" t="n">
         <v>71004</v>
       </c>
       <c r="I5" s="36"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J5" s="36"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="n">
         <v>71004</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="36"/>
       <c r="F6" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
       <c r="I6" s="36"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="n">
         <v>72001</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" s="36"/>
       <c r="H7" s="36"/>
       <c r="I7" s="36"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J7" s="36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="n">
         <v>72002</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" s="36"/>
       <c r="F8" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
       <c r="I8" s="36"/>
+      <c r="J8" s="36" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36"/>
+      <c r="B9" s="36" t="n">
+        <v>72003</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36"/>
+      <c r="B10" s="36" t="n">
+        <v>73001</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="102">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">DamageCoefficient</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve">기본공격1</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_1.AM_Player_LightAttack_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">기본공격2</t>
@@ -489,127 +489,127 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4288,7 +4288,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.97"/>
@@ -4364,165 +4364,165 @@
     <row r="3" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="36"/>
       <c r="B3" s="36" t="n">
-        <v>71001</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
       <c r="E3" s="36"/>
       <c r="F3" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G3" s="36"/>
       <c r="H3" s="36" t="n">
-        <v>71002</v>
-      </c>
-      <c r="I3" s="36"/>
+        <v>71001</v>
+      </c>
+      <c r="I3" s="36" t="n">
+        <v>72001</v>
+      </c>
       <c r="J3" s="36"/>
     </row>
     <row r="4" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36"/>
       <c r="B4" s="36" t="n">
-        <v>71002</v>
+        <v>71001</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" s="36"/>
       <c r="F4" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G4" s="36"/>
       <c r="H4" s="36" t="n">
-        <v>71003</v>
-      </c>
-      <c r="I4" s="36" t="n">
-        <v>72002</v>
-      </c>
+        <v>71002</v>
+      </c>
+      <c r="I4" s="36"/>
       <c r="J4" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="36"/>
       <c r="B5" s="36" t="n">
-        <v>71003</v>
+        <v>71002</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" s="36"/>
       <c r="F5" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G5" s="36"/>
       <c r="H5" s="36" t="n">
-        <v>71004</v>
-      </c>
-      <c r="I5" s="36"/>
+        <v>71003</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>72002</v>
+      </c>
       <c r="J5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="n">
-        <v>71004</v>
+        <v>71003</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E6" s="36"/>
       <c r="F6" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
+      <c r="H6" s="36" t="n">
+        <v>71004</v>
+      </c>
       <c r="I6" s="36"/>
       <c r="J6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="n">
-        <v>72001</v>
+        <v>71004</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G7" s="36"/>
       <c r="H7" s="36"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="36" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="n">
-        <v>72002</v>
+        <v>72001</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E8" s="36"/>
       <c r="F8" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
       <c r="I8" s="36"/>
       <c r="J8" s="36" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="n">
-        <v>72003</v>
+        <v>72002</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
+      <c r="F9" s="36" t="s">
+        <v>85</v>
+      </c>
       <c r="G9" s="36"/>
       <c r="H9" s="36"/>
       <c r="I9" s="36"/>
       <c r="J9" s="36" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="36"/>
       <c r="B10" s="36" t="n">
-        <v>73001</v>
+        <v>72003</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
@@ -4530,6 +4530,26 @@
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
       <c r="J10" s="36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36" t="n">
+        <v>73001</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36" t="n">
         <v>3</v>
       </c>
     </row>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="106">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">DamageCoefficient</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">시작 공격 지정</t>
   </si>
   <si>
     <t xml:space="preserve">기본공격1</t>
@@ -330,6 +330,18 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_ChargeAttack.AM_Player_ChargeAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L”R”R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_3.AM_Player_HeavyAttack_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LR”R”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_4.AM_Player_HeavyAttack_4</t>
   </si>
 </sst>
 </file>
@@ -484,7 +496,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -630,6 +642,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4288,7 +4304,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.97"/>
@@ -4296,11 +4312,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="27.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="126.57"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="32" width="2.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="10.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="10.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="32" width="20.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="32" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="10.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="10.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="20.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4318,7 +4333,7 @@
       </c>
       <c r="E1" s="33"/>
       <c r="F1" s="33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="33" t="n">
         <v>1</v>
@@ -4327,9 +4342,6 @@
         <v>1</v>
       </c>
       <c r="I1" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" s="33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4347,17 +4359,16 @@
         <v>43</v>
       </c>
       <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34" t="s">
+      <c r="F2" s="34" t="s">
         <v>45</v>
       </c>
+      <c r="G2" s="35" t="s">
+        <v>82</v>
+      </c>
       <c r="H2" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="35" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4366,20 +4377,19 @@
       <c r="B3" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="36"/>
+      <c r="C3" s="36" t="s">
+        <v>85</v>
+      </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
-      <c r="F3" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36" t="n">
+        <v>71001</v>
+      </c>
       <c r="H3" s="36" t="n">
-        <v>71001</v>
-      </c>
-      <c r="I3" s="36" t="n">
         <v>72001</v>
       </c>
-      <c r="J3" s="36"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36"/>
@@ -4393,15 +4403,12 @@
         <v>87</v>
       </c>
       <c r="E4" s="36"/>
-      <c r="F4" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36" t="n">
+      <c r="F4" s="36"/>
+      <c r="G4" s="36" t="n">
         <v>71002</v>
       </c>
+      <c r="H4" s="36"/>
       <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="36"/>
@@ -4415,17 +4422,14 @@
         <v>89</v>
       </c>
       <c r="E5" s="36"/>
-      <c r="F5" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36" t="n">
+        <v>71003</v>
+      </c>
       <c r="H5" s="36" t="n">
-        <v>71003</v>
-      </c>
-      <c r="I5" s="36" t="n">
         <v>72002</v>
       </c>
-      <c r="J5" s="36"/>
+      <c r="I5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="36"/>
@@ -4439,15 +4443,12 @@
         <v>91</v>
       </c>
       <c r="E6" s="36"/>
-      <c r="F6" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36" t="n">
+      <c r="F6" s="36"/>
+      <c r="G6" s="36" t="n">
         <v>71004</v>
       </c>
+      <c r="H6" s="36"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="36"/>
@@ -4461,13 +4462,10 @@
         <v>93</v>
       </c>
       <c r="E7" s="36"/>
-      <c r="F7" s="36" t="s">
-        <v>85</v>
-      </c>
+      <c r="F7" s="36"/>
       <c r="G7" s="36"/>
       <c r="H7" s="36"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
@@ -4481,13 +4479,10 @@
         <v>95</v>
       </c>
       <c r="E8" s="36"/>
-      <c r="F8" s="36" t="s">
-        <v>85</v>
-      </c>
+      <c r="F8" s="36"/>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36" t="n">
+      <c r="I8" s="36" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4503,13 +4498,10 @@
         <v>97</v>
       </c>
       <c r="E9" s="36"/>
-      <c r="F9" s="36" t="s">
-        <v>85</v>
-      </c>
+      <c r="F9" s="36"/>
       <c r="G9" s="36"/>
       <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36" t="n">
+      <c r="I9" s="36" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4528,8 +4520,7 @@
       <c r="F10" s="36"/>
       <c r="G10" s="36"/>
       <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36" t="n">
+      <c r="I10" s="36" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4548,9 +4539,52 @@
       <c r="F11" s="36"/>
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36" t="n">
+      <c r="I11" s="36" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="12" s="37" customFormat="true" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36" t="n">
+        <v>72011</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36" t="n">
+        <v>72012</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36" t="n">
+        <v>72012</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36" t="n">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -342,6 +342,18 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_4.AM_Player_HeavyAttack_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좀 더 큰 강공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_5.AM_Player_HeavyAttack_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본공격4 대체 – 위로 띄우는 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_5.AM_Player_LightAttack_5</t>
   </si>
 </sst>
 </file>
@@ -362,19 +374,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="12"/>
@@ -496,7 +505,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -645,10 +654,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -729,37 +734,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -899,7 +904,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.08"/>
@@ -1253,7 +1258,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="8.94"/>
@@ -1505,7 +1510,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R1021"/>
-  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="14.38"/>
@@ -4304,18 +4309,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="27.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="126.57"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="32" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="10.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="10.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="20.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="6.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="30.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="110.12"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="32" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="8.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="17.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4387,7 +4392,7 @@
         <v>71001</v>
       </c>
       <c r="H3" s="36" t="n">
-        <v>72001</v>
+        <v>72003</v>
       </c>
       <c r="I3" s="36"/>
     </row>
@@ -4483,7 +4488,7 @@
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
       <c r="I8" s="36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4502,7 +4507,7 @@
       <c r="G9" s="36"/>
       <c r="H9" s="36"/>
       <c r="I9" s="36" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4521,7 +4526,7 @@
       <c r="G10" s="36"/>
       <c r="H10" s="36"/>
       <c r="I10" s="36" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4540,10 +4545,10 @@
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" s="37" customFormat="true" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="true" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="36"/>
       <c r="B12" s="36" t="n">
         <v>72011</v>
@@ -4563,7 +4568,7 @@
         <v>72012</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4584,7 +4589,45 @@
       <c r="G13" s="36"/>
       <c r="H13" s="36"/>
       <c r="I13" s="36" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36"/>
+      <c r="B14" s="36" t="n">
+        <v>72004</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="36"/>
+      <c r="B15" s="36" t="n">
+        <v>71011</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -281,15 +281,15 @@
     <t xml:space="preserve">DamageCoefficient</t>
   </si>
   <si>
+    <t xml:space="preserve">시작 공격 지정</t>
+  </si>
+  <si>
     <t xml:space="preserve">기본공격1</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_1.AM_Player_LightAttack_1</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t xml:space="preserve">기본공격2</t>
   </si>
   <si>
@@ -330,6 +330,30 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_ChargeAttack.AM_Player_ChargeAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L”R”R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_3.AM_Player_HeavyAttack_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LR”R”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_4.AM_Player_HeavyAttack_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좀 더 큰 강공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/HeavyAttack/AM_Player_HeavyAttack_5.AM_Player_HeavyAttack_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본공격4 대체 – 위로 띄우는 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/LightAttack/AM_Player_LightAttack_5.AM_Player_LightAttack_5</t>
   </si>
 </sst>
 </file>
@@ -350,19 +374,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="12"/>
@@ -489,127 +510,127 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -713,37 +734,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -883,7 +904,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.08"/>
@@ -1237,7 +1258,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="8.94"/>
@@ -1489,7 +1510,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R1021"/>
-  <sheetFormatPr defaultColWidth="7.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="14.38"/>
@@ -4288,19 +4309,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="12.8046875" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="27.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="126.57"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="12.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="32" width="2.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="10.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="10.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="32" width="20.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="32" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="6.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="30.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="110.12"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="5" style="32" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="32" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="32" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="32" width="8.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="32" width="17.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4318,7 +4338,7 @@
       </c>
       <c r="E1" s="33"/>
       <c r="F1" s="33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="33" t="n">
         <v>1</v>
@@ -4327,9 +4347,6 @@
         <v>1</v>
       </c>
       <c r="I1" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1" s="33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4347,190 +4364,270 @@
         <v>43</v>
       </c>
       <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34" t="s">
+      <c r="F2" s="34" t="s">
         <v>45</v>
       </c>
+      <c r="G2" s="35" t="s">
+        <v>82</v>
+      </c>
       <c r="H2" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="J2" s="35" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="36"/>
       <c r="B3" s="36" t="n">
-        <v>71001</v>
+        <v>0</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="36" t="s">
-        <v>86</v>
-      </c>
+      <c r="D3" s="36"/>
       <c r="E3" s="36"/>
-      <c r="F3" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36" t="n">
+        <v>71001</v>
+      </c>
       <c r="H3" s="36" t="n">
-        <v>71002</v>
+        <v>72003</v>
       </c>
       <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
     </row>
     <row r="4" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36"/>
       <c r="B4" s="36" t="n">
+        <v>71001</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36" t="n">
         <v>71002</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36" t="n">
-        <v>71003</v>
-      </c>
-      <c r="I4" s="36" t="n">
-        <v>72002</v>
-      </c>
-      <c r="J4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="36"/>
       <c r="B5" s="36" t="n">
+        <v>71002</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36" t="n">
         <v>71003</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="36"/>
       <c r="H5" s="36" t="n">
-        <v>71004</v>
+        <v>72002</v>
       </c>
       <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="n">
+        <v>71003</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36" t="n">
         <v>71004</v>
       </c>
-      <c r="C6" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="36"/>
       <c r="H6" s="36"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="n">
-        <v>72001</v>
+        <v>71004</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7" s="36"/>
-      <c r="F7" s="36" t="s">
-        <v>87</v>
-      </c>
+      <c r="F7" s="36"/>
       <c r="G7" s="36"/>
       <c r="H7" s="36"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="36" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="8" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="n">
-        <v>72002</v>
+        <v>72001</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E8" s="36"/>
-      <c r="F8" s="36" t="s">
-        <v>87</v>
-      </c>
+      <c r="F8" s="36"/>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36" t="n">
+      <c r="I8" s="36" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="n">
-        <v>72003</v>
+        <v>72002</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
       <c r="G9" s="36"/>
       <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I9" s="36" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="36"/>
       <c r="B10" s="36" t="n">
-        <v>73001</v>
+        <v>72003</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
       <c r="G10" s="36"/>
       <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36" t="n">
-        <v>3</v>
+      <c r="I10" s="36" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36"/>
+      <c r="B11" s="36" t="n">
+        <v>73001</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="true" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36"/>
+      <c r="B12" s="36" t="n">
+        <v>72011</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36" t="n">
+        <v>72012</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36" t="n">
+        <v>72012</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36"/>
+      <c r="B14" s="36" t="n">
+        <v>72004</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="36"/>
+      <c r="B15" s="36" t="n">
+        <v>71011</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/Action.xlsx
+++ b/BADesign/Excel/Action.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="114">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -113,6 +113,15 @@
     <t xml:space="preserve">Dodge</t>
   </si>
   <si>
+    <t xml:space="preserve">Heal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UseItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UseConsumable</t>
+  </si>
+  <si>
     <t xml:space="preserve">설명</t>
   </si>
   <si>
@@ -246,6 +255,9 @@
   </si>
   <si>
     <t xml:space="preserve">Loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Character/Player/Animation/Montages/Heal/AM_Player_DrinkPotion.AM_Player_DrinkPotion</t>
   </si>
   <si>
     <t xml:space="preserve">ActionAnimationTid</t>
@@ -903,7 +915,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultColWidth="11.62109375" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.11"/>
@@ -1241,6 +1253,38 @@
         <v>1</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>10031</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1257,7 +1301,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="7.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.6"/>
@@ -1317,31 +1361,31 @@
         <v>2</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1350,22 +1394,22 @@
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J3" s="11" t="n">
         <v>10001</v>
@@ -1380,22 +1424,22 @@
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J4" s="11" t="n">
         <v>10002</v>
@@ -1410,22 +1454,22 @@
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>10011</v>
@@ -1440,22 +1484,22 @@
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J6" s="11" t="n">
         <v>10021</v>
@@ -1469,28 +1513,57 @@
         <v>20022</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>10022</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="10" t="n">
+        <v>20031</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>10031</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1577,34 +1650,34 @@
         <v>2</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D2" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>32</v>
-      </c>
       <c r="F2" s="18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -1622,16 +1695,16 @@
         <v>10021</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H3" s="20"/>
       <c r="I3" s="20" t="n">
@@ -1662,16 +1735,16 @@
         <v>10021</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="20" t="n">
@@ -1702,16 +1775,16 @@
         <v>10021</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H5" s="14"/>
       <c r="I5" s="14" t="n">
@@ -1742,16 +1815,16 @@
         <v>10021</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="20" t="n">
@@ -1782,16 +1855,16 @@
         <v>10021</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14" t="n">
@@ -1822,16 +1895,16 @@
         <v>10021</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="20" t="n">
@@ -1862,16 +1935,16 @@
         <v>10021</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="n">
@@ -1896,16 +1969,16 @@
         <v>10021</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="20" t="n">
@@ -1930,16 +2003,16 @@
         <v>10021</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14" t="n">
@@ -1964,16 +2037,16 @@
         <v>10022</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="16" t="n">
@@ -1998,16 +2071,16 @@
         <v>10022</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="16" t="n">
@@ -2032,16 +2105,16 @@
         <v>10022</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="23" t="n">
@@ -2066,16 +2139,16 @@
         <v>10022</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16" t="n">
@@ -2100,16 +2173,16 @@
         <v>10022</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="23" t="n">
@@ -2134,16 +2207,16 @@
         <v>10022</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H17" s="16"/>
       <c r="I17" s="16" t="n">
@@ -2168,16 +2241,16 @@
         <v>10022</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="23" t="n">
@@ -2202,16 +2275,16 @@
         <v>10022</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H19" s="16"/>
       <c r="I19" s="16" t="n">
@@ -2236,16 +2309,16 @@
         <v>10022</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="23" t="n">
@@ -2270,19 +2343,19 @@
         <v>10011</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I21" s="20" t="n">
         <v>1</v>
@@ -2295,7 +2368,38 @@
       </c>
       <c r="L21" s="20"/>
     </row>
-    <row r="22" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="n">
+        <v>30071</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="23" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3354,19 +3458,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3378,7 +3482,7 @@
         <v>30021</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>0.1</v>
@@ -3397,7 +3501,7 @@
         <v>30021</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E4" s="30" t="n">
         <v>0</v>
@@ -3416,7 +3520,7 @@
         <v>30021</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>0.55</v>
@@ -3434,7 +3538,7 @@
         <v>30022</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E6" s="29" t="n">
         <v>0.1</v>
@@ -3451,7 +3555,7 @@
         <v>30022</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E7" s="30" t="n">
         <v>0</v>
@@ -3468,7 +3572,7 @@
         <v>30022</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E8" s="29" t="n">
         <v>0.55</v>
@@ -3485,7 +3589,7 @@
         <v>30023</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E9" s="29" t="n">
         <v>0.1</v>
@@ -3502,7 +3606,7 @@
         <v>30023</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E10" s="30" t="n">
         <v>0</v>
@@ -3519,7 +3623,7 @@
         <v>30023</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E11" s="29" t="n">
         <v>0.55</v>
@@ -3536,7 +3640,7 @@
         <v>30024</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E12" s="29" t="n">
         <v>0.1</v>
@@ -3553,7 +3657,7 @@
         <v>30024</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>0</v>
@@ -3570,7 +3674,7 @@
         <v>30024</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E14" s="29" t="n">
         <v>0.55</v>
@@ -3587,7 +3691,7 @@
         <v>30025</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E15" s="29" t="n">
         <v>0.1</v>
@@ -3604,7 +3708,7 @@
         <v>30025</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E16" s="30" t="n">
         <v>0</v>
@@ -3621,7 +3725,7 @@
         <v>30025</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E17" s="29" t="n">
         <v>0.55</v>
@@ -3638,7 +3742,7 @@
         <v>30026</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E18" s="29" t="n">
         <v>0.1</v>
@@ -3655,7 +3759,7 @@
         <v>30026</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0</v>
@@ -3672,7 +3776,7 @@
         <v>30026</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>0.55</v>
@@ -3689,7 +3793,7 @@
         <v>30027</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E21" s="29" t="n">
         <v>0.1</v>
@@ -3706,7 +3810,7 @@
         <v>30027</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>0</v>
@@ -3723,7 +3827,7 @@
         <v>30027</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E23" s="29" t="n">
         <v>0.55</v>
@@ -3740,7 +3844,7 @@
         <v>30028</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E24" s="29" t="n">
         <v>0.1</v>
@@ -3757,7 +3861,7 @@
         <v>30028</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>0</v>
@@ -3774,7 +3878,7 @@
         <v>30028</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E26" s="29" t="n">
         <v>0.55</v>
@@ -3791,7 +3895,7 @@
         <v>30029</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E27" s="29" t="n">
         <v>0.1</v>
@@ -3808,7 +3912,7 @@
         <v>30029</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>0</v>
@@ -3825,7 +3929,7 @@
         <v>30029</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E29" s="29" t="n">
         <v>0.55</v>
@@ -3842,7 +3946,7 @@
         <v>30030</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E30" s="29" t="n">
         <v>0.1</v>
@@ -3859,7 +3963,7 @@
         <v>30030</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>0</v>
@@ -3876,7 +3980,7 @@
         <v>30030</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E32" s="29" t="n">
         <v>0.55</v>
@@ -3893,7 +3997,7 @@
         <v>30031</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>0.1</v>
@@ -3910,7 +4014,7 @@
         <v>30031</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E34" s="30" t="n">
         <v>0</v>
@@ -3927,7 +4031,7 @@
         <v>30031</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>0.55</v>
@@ -3944,7 +4048,7 @@
         <v>30032</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E36" s="29" t="n">
         <v>0.1</v>
@@ -3961,7 +4065,7 @@
         <v>30032</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E37" s="30" t="n">
         <v>0</v>
@@ -3978,7 +4082,7 @@
         <v>30032</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E38" s="29" t="n">
         <v>0.55</v>
@@ -3995,7 +4099,7 @@
         <v>30033</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>0.1</v>
@@ -4012,7 +4116,7 @@
         <v>30033</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E40" s="30" t="n">
         <v>0</v>
@@ -4029,7 +4133,7 @@
         <v>30033</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>0.55</v>
@@ -4046,7 +4150,7 @@
         <v>30034</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E42" s="29" t="n">
         <v>0.1</v>
@@ -4063,7 +4167,7 @@
         <v>30034</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E43" s="30" t="n">
         <v>0</v>
@@ -4080,7 +4184,7 @@
         <v>30034</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E44" s="29" t="n">
         <v>0.55</v>
@@ -4097,7 +4201,7 @@
         <v>30035</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E45" s="29" t="n">
         <v>0.1</v>
@@ -4114,7 +4218,7 @@
         <v>30035</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E46" s="30" t="n">
         <v>0</v>
@@ -4131,7 +4235,7 @@
         <v>30035</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E47" s="29" t="n">
         <v>0.55</v>
@@ -4148,7 +4252,7 @@
         <v>30036</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E48" s="29" t="n">
         <v>0.1</v>
@@ -4165,7 +4269,7 @@
         <v>30036</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E49" s="30" t="n">
         <v>0</v>
@@ -4182,7 +4286,7 @@
         <v>30036</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E50" s="29" t="n">
         <v>0.55</v>
@@ -4199,7 +4303,7 @@
         <v>30037</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E51" s="29" t="n">
         <v>0.1</v>
@@ -4216,7 +4320,7 @@
         <v>30037</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E52" s="30" t="n">
         <v>0</v>
@@ -4233,7 +4337,7 @@
         <v>30037</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E53" s="29" t="n">
         <v>0.55</v>
@@ -4250,7 +4354,7 @@
         <v>30038</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E54" s="29" t="n">
         <v>0.1</v>
@@ -4267,7 +4371,7 @@
         <v>30038</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E55" s="30" t="n">
         <v>0</v>
@@ -4284,7 +4388,7 @@
         <v>30038</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E56" s="29" t="n">
         <v>0.55</v>
@@ -4358,23 +4462,23 @@
         <v>2</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E2" s="34"/>
       <c r="F2" s="34" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H2" s="35" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4383,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -4402,10 +4506,10 @@
         <v>71001</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E4" s="36"/>
       <c r="F4" s="36"/>
@@ -4421,10 +4525,10 @@
         <v>71002</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E5" s="36"/>
       <c r="F5" s="36"/>
@@ -4442,10 +4546,10 @@
         <v>71003</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E6" s="36"/>
       <c r="F6" s="36"/>
@@ -4461,10 +4565,10 @@
         <v>71004</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
@@ -4478,10 +4582,10 @@
         <v>72001</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
@@ -4497,10 +4601,10 @@
         <v>72002</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -4516,10 +4620,10 @@
         <v>72003</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
@@ -4535,10 +4639,10 @@
         <v>73001</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
@@ -4554,10 +4658,10 @@
         <v>72011</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="36" t="n">
@@ -4577,10 +4681,10 @@
         <v>72012</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36" t="n">
@@ -4598,10 +4702,10 @@
         <v>72004</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
@@ -4617,10 +4721,10 @@
         <v>71011</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
